--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Dreamland Gran Canaria.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Dreamland Gran Canaria.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2086.88</v>
+        <v>2396.88</v>
       </c>
       <c r="C2" t="n">
-        <v>2078.38</v>
+        <v>2387.52</v>
       </c>
       <c r="D2" t="n">
-        <v>108.690422348175</v>
+        <v>109.0252647098244</v>
       </c>
       <c r="E2" t="n">
-        <v>115.0415227244296</v>
+        <v>114.7634365366573</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5168282943525385</v>
+        <v>0.5224775224775224</v>
       </c>
       <c r="G2" t="n">
-        <v>0.143889142066265</v>
+        <v>0.1450304860001184</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2855701311806256</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2549914432401597</v>
+        <v>0.2552447552447553</v>
       </c>
       <c r="J2" t="n">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="L2" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="M2" t="n">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="N2" t="n">
-        <v>735</v>
+        <v>834</v>
       </c>
       <c r="O2" t="n">
-        <v>1007</v>
+        <v>1129</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5744438106103822</v>
+        <v>0.563936063936064</v>
       </c>
       <c r="Q2" t="n">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2156303479749002</v>
+        <v>0.2102897102897103</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="U2" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1403308613804906</v>
+        <v>0.1448551448551449</v>
       </c>
       <c r="W2" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="X2" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08956075299486595</v>
+        <v>0.0924075924075924</v>
       </c>
       <c r="Z2" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="AA2" t="n">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3377067883628066</v>
+        <v>0.3391608391608392</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7298907646474677</v>
+        <v>0.7387068201948627</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4656084656084656</v>
+        <v>0.4726840855106889</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3089430894308943</v>
+        <v>0.3068965517241379</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3375796178343949</v>
+        <v>0.3567567567567568</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3226351351351351</v>
+        <v>0.3298969072164948</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.459781529294935</v>
+        <v>1.477413640389725</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.6137931034482759</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9773030707610146</v>
+        <v>1.006944444444444</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.7880952380952381</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.003533568904594</v>
+        <v>0.9967320261437909</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.602941176470588</v>
+        <v>1.566265060240964</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.278592375366569</v>
+        <v>1.252551020408163</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.140762463343108</v>
+        <v>5.107142857142857</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.419354838709677</v>
+        <v>6.35969387755102</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.53142857142858</v>
+        <v>74.9025</v>
       </c>
       <c r="C3" t="n">
-        <v>74.22785714285715</v>
+        <v>74.61</v>
       </c>
       <c r="D3" t="n">
-        <v>108.690422348175</v>
+        <v>109.0252647098244</v>
       </c>
       <c r="E3" t="n">
-        <v>115.0415227244296</v>
+        <v>114.7634365366573</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5168282943525385</v>
+        <v>0.5224775224775224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.143889142066265</v>
+        <v>0.1450304860001184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2855701311806257</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2549914432401597</v>
+        <v>0.2552447552447553</v>
       </c>
       <c r="J3" t="n">
-        <v>10.14285714285714</v>
+        <v>10.34375</v>
       </c>
       <c r="K3" t="n">
-        <v>10.14285714285714</v>
+        <v>9.53125</v>
       </c>
       <c r="L3" t="n">
-        <v>3.892857142857143</v>
+        <v>4.0625</v>
       </c>
       <c r="M3" t="n">
-        <v>11.35714285714286</v>
+        <v>11.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>26.25</v>
+        <v>26.0625</v>
       </c>
       <c r="O3" t="n">
-        <v>35.96428571428572</v>
+        <v>35.28125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5744438106103823</v>
+        <v>0.563936063936064</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.285714285714286</v>
+        <v>6.21875</v>
       </c>
       <c r="R3" t="n">
-        <v>13.5</v>
+        <v>13.15625</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2156303479749002</v>
+        <v>0.2102897102897103</v>
       </c>
       <c r="T3" t="n">
-        <v>2.714285714285714</v>
+        <v>2.78125</v>
       </c>
       <c r="U3" t="n">
-        <v>8.785714285714286</v>
+        <v>9.0625</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1403308613804906</v>
+        <v>0.1448551448551449</v>
       </c>
       <c r="W3" t="n">
-        <v>1.892857142857143</v>
+        <v>2.0625</v>
       </c>
       <c r="X3" t="n">
-        <v>5.607142857142857</v>
+        <v>5.78125</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08956075299486595</v>
+        <v>0.0924075924075924</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.821428571428571</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.14285714285714</v>
+        <v>21.21875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3377067883628066</v>
+        <v>0.3391608391608392</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7298907646474677</v>
+        <v>0.7387068201948627</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4656084656084656</v>
+        <v>0.4726840855106889</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3089430894308943</v>
+        <v>0.3068965517241379</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3375796178343949</v>
+        <v>0.3567567567567568</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3226351351351351</v>
+        <v>0.3298969072164948</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.459781529294935</v>
+        <v>1.477413640389725</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.6137931034482759</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9773030707610145</v>
+        <v>1.006944444444444</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7553191489361701</v>
+        <v>0.7880952380952381</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.003533568904593</v>
+        <v>0.9967320261437909</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.602941176470588</v>
+        <v>1.566265060240964</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.278592375366569</v>
+        <v>1.252551020408163</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.140762463343108</v>
+        <v>5.107142857142857</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.419354838709677</v>
+        <v>6.35969387755102</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2069.880000000001</v>
+        <v>2378.16</v>
       </c>
       <c r="C4" t="n">
-        <v>2078.38</v>
+        <v>2387.52</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0415227244296</v>
+        <v>114.7634365366573</v>
       </c>
       <c r="E4" t="n">
-        <v>108.690422348175</v>
+        <v>109.0252647098244</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5558180744240993</v>
+        <v>0.5538891713268937</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1596006587771873</v>
+        <v>0.1548581204648693</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3112078346028291</v>
+        <v>0.3124415341440599</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3006497341996456</v>
+        <v>0.2852058973055414</v>
       </c>
       <c r="J4" t="n">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="L4" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="M4" t="n">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="N4" t="n">
-        <v>806</v>
+        <v>915</v>
       </c>
       <c r="O4" t="n">
-        <v>1059</v>
+        <v>1215</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6255168340224454</v>
+        <v>0.617691916624301</v>
       </c>
       <c r="Q4" t="n">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="R4" t="n">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2049616066154755</v>
+        <v>0.2053889171326894</v>
       </c>
       <c r="T4" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="U4" t="n">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1281748375664501</v>
+        <v>0.14489069649212</v>
       </c>
       <c r="W4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="X4" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1015948021264028</v>
+        <v>0.09303507880020336</v>
       </c>
       <c r="Z4" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="AA4" t="n">
-        <v>550</v>
+        <v>619</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3248670998227998</v>
+        <v>0.3146924250127097</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.76109537299339</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4553314121037464</v>
+        <v>0.4554455445544555</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3732718894009217</v>
+        <v>0.3824561403508772</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3779069767441861</v>
+        <v>0.3825136612021858</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3727272727272727</v>
+        <v>0.3634894991922455</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.52219074598678</v>
+        <v>1.506172839506173</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7465437788018433</v>
+        <v>0.7649122807017544</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.121883656509695</v>
+        <v>1.103491271820449</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8856304985337243</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9440559440559441</v>
+        <v>0.9191616766467066</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.465116279069767</v>
+        <v>1.474226804123711</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.231382978723404</v>
+        <v>1.245238095238095</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.502659574468085</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.73404255319149</v>
+        <v>5.928571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.92428571428573</v>
+        <v>74.31750000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>74.22785714285715</v>
+        <v>74.61</v>
       </c>
       <c r="D5" t="n">
-        <v>115.0415227244296</v>
+        <v>114.7634365366573</v>
       </c>
       <c r="E5" t="n">
-        <v>108.690422348175</v>
+        <v>109.0252647098244</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5558180744240991</v>
+        <v>0.5538891713268937</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1596006587771873</v>
+        <v>0.1548581204648693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3112078346028291</v>
+        <v>0.3124415341440599</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3006497341996456</v>
+        <v>0.2852058973055414</v>
       </c>
       <c r="J5" t="n">
-        <v>10.78571428571429</v>
+        <v>10.75</v>
       </c>
       <c r="K5" t="n">
-        <v>9.642857142857142</v>
+        <v>9.59375</v>
       </c>
       <c r="L5" t="n">
-        <v>4.5</v>
+        <v>4.46875</v>
       </c>
       <c r="M5" t="n">
-        <v>12.32142857142857</v>
+        <v>12.09375</v>
       </c>
       <c r="N5" t="n">
-        <v>28.78571428571428</v>
+        <v>28.59375</v>
       </c>
       <c r="O5" t="n">
-        <v>37.82142857142857</v>
+        <v>37.96875</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6255168340224453</v>
+        <v>0.617691916624301</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.642857142857143</v>
+        <v>5.75</v>
       </c>
       <c r="R5" t="n">
-        <v>12.39285714285714</v>
+        <v>12.625</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2049616066154755</v>
+        <v>0.2053889171326894</v>
       </c>
       <c r="T5" t="n">
-        <v>2.892857142857143</v>
+        <v>3.40625</v>
       </c>
       <c r="U5" t="n">
-        <v>7.75</v>
+        <v>8.90625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1281748375664501</v>
+        <v>0.14489069649212</v>
       </c>
       <c r="W5" t="n">
-        <v>2.321428571428572</v>
+        <v>2.1875</v>
       </c>
       <c r="X5" t="n">
-        <v>6.142857142857143</v>
+        <v>5.71875</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1015948021264028</v>
+        <v>0.09303507880020336</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.321428571428571</v>
+        <v>7.03125</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.64285714285714</v>
+        <v>19.34375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3248670998227998</v>
+        <v>0.3146924250127097</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.76109537299339</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4553314121037464</v>
+        <v>0.4554455445544555</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3732718894009217</v>
+        <v>0.3824561403508772</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3779069767441861</v>
+        <v>0.3825136612021858</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3727272727272727</v>
+        <v>0.3634894991922455</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.52219074598678</v>
+        <v>1.506172839506173</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7465437788018433</v>
+        <v>0.7649122807017544</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.121883656509695</v>
+        <v>1.103491271820449</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8856304985337243</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9440559440559441</v>
+        <v>0.9191616766467066</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.465116279069767</v>
+        <v>1.474226804123711</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.231382978723404</v>
+        <v>1.245238095238095</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.502659574468085</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.73404255319149</v>
+        <v>5.928571428571429</v>
       </c>
     </row>
     <row r="7">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -1437,10 +1437,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1470,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
         <v>3</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1534,41 +1534,41 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>57:00</t>
+          <t>58:44</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>13.4</v>
+        <v>14.28</v>
       </c>
       <c r="AP8" t="n">
         <v>0.375</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.444</v>
+        <v>0.489</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.821</v>
+        <v>0.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>464</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="H9" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="I9" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="J9" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
         <v>17</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
         <v>13</v>
@@ -1620,114 +1620,114 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="S9" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="T9" t="n">
-        <v>358</v>
+        <v>437</v>
       </c>
       <c r="U9" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="V9" t="n">
         <v>32</v>
       </c>
       <c r="W9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="Z9" t="n">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.832</v>
+        <v>0.837</v>
       </c>
       <c r="AB9" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AC9" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.493</v>
+        <v>0.506</v>
       </c>
       <c r="AE9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI9" t="n">
         <v>22</v>
       </c>
-      <c r="AF9" t="n">
-        <v>62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>21</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AM9" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>721:46</t>
+        </is>
+      </c>
+      <c r="AO9" t="n">
+        <v>424.2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0.281</v>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>610:54</t>
-        </is>
-      </c>
-      <c r="AO9" t="n">
-        <v>359.64</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.688</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.279</v>
-      </c>
       <c r="AW9" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H10" t="n">
         <v>13</v>
@@ -1761,13 +1761,13 @@
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
@@ -1779,40 +1779,40 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="U10" t="n">
         <v>17</v>
       </c>
       <c r="V10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
@@ -1827,66 +1827,66 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.167</v>
+        <v>0.111</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.375</v>
+        <v>0.423</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>213:15</t>
+          <t>242:21</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>71.8</v>
+        <v>79.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.432</v>
+        <v>0.47</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.472</v>
+        <v>0.501</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.891</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.056</v>
+        <v>0.063</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.22</v>
+        <v>0.197</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.053</v>
+        <v>0.057</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="11">
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
         <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="n">
         <v>22</v>
@@ -1920,13 +1920,13 @@
         <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T11" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U11" t="n">
         <v>13</v>
@@ -1968,19 +1968,19 @@
         <v>40</v>
       </c>
       <c r="Z11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.678</v>
+        <v>0.656</v>
       </c>
       <c r="AB11" t="n">
         <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -1992,13 +1992,13 @@
         <v>0.333</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.4</v>
+        <v>0.455</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>369:22</t>
+          <t>392:29</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>172.2</v>
+        <v>178.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.825</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.151</v>
+        <v>0.157</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.165</v>
+        <v>0.161</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.885</v>
+        <v>1.929</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.221</v>
+        <v>0.217</v>
       </c>
       <c r="AW11" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AX11" t="n">
         <v>0.077</v>
       </c>
-      <c r="AX11" t="n">
-        <v>0.083</v>
-      </c>
       <c r="AY11" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -2097,22 +2097,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="S12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -2124,13 +2124,13 @@
         <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Z12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.604</v>
+        <v>0.608</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
@@ -2163,48 +2163,48 @@
         <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.268</v>
+        <v>0.253</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>655:57</t>
+          <t>704:44</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>177.6</v>
+        <v>188.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.363</v>
+        <v>0.348</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.416</v>
+        <v>0.406</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.631</v>
+        <v>0.605</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.242</v>
+        <v>0.255</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.231</v>
+        <v>0.238</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.186</v>
+        <v>2.083</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AX12" t="n">
         <v>0.043</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
@@ -2214,156 +2214,156 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
+        <v>94</v>
+      </c>
+      <c r="F13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" t="n">
+        <v>71</v>
+      </c>
+      <c r="I13" t="n">
+        <v>88</v>
+      </c>
+      <c r="J13" t="n">
+        <v>72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>96</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18</v>
+      </c>
+      <c r="M13" t="n">
+        <v>40</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" t="n">
         <v>83</v>
       </c>
-      <c r="F13" t="n">
-        <v>48</v>
-      </c>
-      <c r="G13" t="n">
-        <v>137</v>
-      </c>
-      <c r="H13" t="n">
-        <v>67</v>
-      </c>
-      <c r="I13" t="n">
-        <v>84</v>
-      </c>
-      <c r="J13" t="n">
-        <v>63</v>
-      </c>
-      <c r="K13" t="n">
-        <v>85</v>
-      </c>
-      <c r="L13" t="n">
-        <v>14</v>
-      </c>
-      <c r="M13" t="n">
-        <v>36</v>
-      </c>
-      <c r="N13" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>49</v>
-      </c>
-      <c r="R13" t="n">
-        <v>75</v>
-      </c>
       <c r="S13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="U13" t="n">
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Z13" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.803</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.519</v>
+        <v>0.548</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.222</v>
+        <v>0.19</v>
       </c>
       <c r="AH13" t="n">
         <v>8</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>764:54</t>
+          <t>880:43</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>305.96</v>
+        <v>337.72</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.601</v>
+        <v>0.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.004</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.305</v>
+        <v>0.291</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.286</v>
+        <v>1.309</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.19</v>
+        <v>0.183</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="14">
@@ -2513,16 +2513,16 @@
         <v>1.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.166</v>
+        <v>0.163</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
@@ -2532,40 +2532,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S15" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="T15" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="U15" t="n">
         <v>3</v>
@@ -2595,28 +2595,28 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="AB15" t="n">
         <v>3</v>
       </c>
-      <c r="Y15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -2637,51 +2637,51 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>133:51</t>
+          <t>197:02</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>63.6</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.372</v>
+        <v>0.446</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.428</v>
+        <v>0.518</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.613</v>
+        <v>0.72</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.283</v>
+        <v>0.305</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.256</v>
+        <v>0.391</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.222</v>
+        <v>1.12</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.226</v>
+        <v>0.199</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.165</v>
+        <v>0.178</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="16">
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H16" t="n">
+        <v>26</v>
+      </c>
+      <c r="I16" t="n">
+        <v>34</v>
+      </c>
+      <c r="J16" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" t="n">
+        <v>122</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>27</v>
+      </c>
+      <c r="N16" t="n">
         <v>23</v>
       </c>
-      <c r="I16" t="n">
-        <v>31</v>
-      </c>
-      <c r="J16" t="n">
-        <v>33</v>
-      </c>
-      <c r="K16" t="n">
-        <v>94</v>
-      </c>
-      <c r="L16" t="n">
-        <v>33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>24</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="S16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T16" t="n">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="U16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V16" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="W16" t="n">
         <v>16</v>
@@ -2760,87 +2760,87 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Z16" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.754</v>
+        <v>0.763</v>
       </c>
       <c r="AB16" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI16" t="n">
         <v>27</v>
       </c>
-      <c r="AC16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AJ16" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AK16" t="n">
         <v>28</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>24</v>
-      </c>
       <c r="AL16" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.453</v>
+        <v>0.424</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>595:54</t>
+          <t>699:52</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>216.64</v>
+        <v>259.96</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.637</v>
+        <v>0.63</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.651</v>
+        <v>0.645</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.159</v>
+        <v>1.166</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.375</v>
+        <v>1.48</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.173</v>
+        <v>0.177</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.193</v>
+        <v>0.21</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="17">
@@ -2850,100 +2850,100 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R17" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="S17" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="T17" t="n">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V17" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AA17" t="n">
         <v>0.736</v>
       </c>
       <c r="AB17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
         <v>9</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2958,48 +2958,48 @@
         <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.269</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>564:57</t>
+          <t>629:53</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>228</v>
+        <v>251.08</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.552</v>
+        <v>0.553</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.022</v>
+        <v>1.024</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="18">
@@ -3149,970 +3149,970 @@
         <v>0.625</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#23 K. KUATH</t>
+          <t>#21 B. JEFFERSON</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>171</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
+        <v>17</v>
+      </c>
+      <c r="H19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="n">
-        <v>23</v>
-      </c>
       <c r="I19" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL19" t="n">
         <v>12</v>
       </c>
-      <c r="K19" t="n">
-        <v>51</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34</v>
-      </c>
-      <c r="M19" t="n">
-        <v>9</v>
-      </c>
-      <c r="N19" t="n">
-        <v>51</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>20</v>
-      </c>
-      <c r="R19" t="n">
-        <v>50</v>
-      </c>
-      <c r="S19" t="n">
-        <v>48</v>
-      </c>
-      <c r="T19" t="n">
-        <v>236</v>
-      </c>
-      <c r="U19" t="n">
-        <v>17</v>
-      </c>
-      <c r="V19" t="n">
-        <v>31</v>
-      </c>
-      <c r="W19" t="n">
-        <v>7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>52</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1</v>
-      </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>399:43</t>
+          <t>56:21</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>157.88</v>
+        <v>25.88</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.643</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.62</v>
+        <v>0.503</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.083</v>
+        <v>0.85</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.127</v>
+        <v>0.155</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.2</v>
+        <v>0.048</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.187</v>
+        <v>0.219</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.156</v>
+        <v>0.064</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#24 B. ANGOLA</t>
+          <t>#23 K. KUATH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D20" t="n">
+        <v>75</v>
+      </c>
+      <c r="E20" t="n">
+        <v>115</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="n">
+        <v>52</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13</v>
+      </c>
+      <c r="K20" t="n">
+        <v>51</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>51</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20</v>
+      </c>
+      <c r="R20" t="n">
+        <v>52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>48</v>
+      </c>
+      <c r="T20" t="n">
+        <v>238</v>
+      </c>
+      <c r="U20" t="n">
         <v>17</v>
       </c>
-      <c r="E20" t="n">
-        <v>46</v>
-      </c>
-      <c r="F20" t="n">
-        <v>22</v>
-      </c>
-      <c r="G20" t="n">
-        <v>69</v>
-      </c>
-      <c r="H20" t="n">
-        <v>32</v>
-      </c>
-      <c r="I20" t="n">
-        <v>46</v>
-      </c>
-      <c r="J20" t="n">
-        <v>27</v>
-      </c>
-      <c r="K20" t="n">
-        <v>23</v>
-      </c>
-      <c r="L20" t="n">
-        <v>15</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>23</v>
-      </c>
-      <c r="R20" t="n">
-        <v>38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>45</v>
-      </c>
-      <c r="T20" t="n">
-        <v>109</v>
-      </c>
-      <c r="U20" t="n">
-        <v>28</v>
-      </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="W20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="n">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.672</v>
+        <v>0.658</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC20" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.188</v>
+        <v>0.462</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
         <v>0.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>291:27</t>
+          <t>403:57</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>158.24</v>
+        <v>158.88</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.435</v>
+        <v>0.647</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.488</v>
+        <v>0.623</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.834</v>
+        <v>1.089</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.145</v>
+        <v>0.126</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.278</v>
+        <v>0.198</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.174</v>
+        <v>0.65</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.258</v>
+        <v>0.188</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.058</v>
+        <v>0.097</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.097</v>
+        <v>0.152</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.036</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#25 C. METU</t>
+          <t>#24 B. ANGOLA</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" t="n">
+        <v>132</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>69</v>
+      </c>
+      <c r="H21" t="n">
+        <v>32</v>
+      </c>
+      <c r="I21" t="n">
+        <v>46</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27</v>
+      </c>
+      <c r="K21" t="n">
+        <v>23</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23</v>
+      </c>
+      <c r="R21" t="n">
+        <v>38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>109</v>
+      </c>
+      <c r="U21" t="n">
+        <v>28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
         <v>6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>87</v>
-      </c>
-      <c r="D21" t="n">
-        <v>19</v>
-      </c>
-      <c r="E21" t="n">
-        <v>38</v>
-      </c>
-      <c r="F21" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" t="n">
-        <v>23</v>
-      </c>
-      <c r="H21" t="n">
-        <v>22</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>26</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>15</v>
-      </c>
-      <c r="R21" t="n">
-        <v>12</v>
-      </c>
-      <c r="S21" t="n">
-        <v>24</v>
-      </c>
-      <c r="T21" t="n">
-        <v>86</v>
-      </c>
-      <c r="U21" t="n">
-        <v>18</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>10</v>
       </c>
       <c r="X21" t="n">
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="Z21" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.838</v>
+        <v>0.672</v>
       </c>
       <c r="AB21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
         <v>16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5</v>
+        <v>0.188</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.154</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.6</v>
+        <v>0.357</v>
       </c>
       <c r="AK21" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.333</v>
+        <v>0.309</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>145:34</t>
+          <t>291:27</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>88.31999999999999</v>
+        <v>158.24</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.533</v>
+        <v>0.435</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.593</v>
+        <v>0.488</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.985</v>
+        <v>0.834</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.17</v>
+        <v>0.145</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.361</v>
+        <v>0.278</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.4</v>
+        <v>1.174</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.288</v>
+        <v>0.259</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.219</v>
+        <v>0.095</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.008</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>#27 M. MITEO</t>
+          <t>#25 C. METU</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>03:36</t>
+          <t>258:04</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>0.88</v>
+        <v>141.16</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.136</v>
+        <v>0.593</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.273</v>
+        <v>0.985</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.116</v>
+        <v>0.261</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.34</v>
+        <v>0.182</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>#30 K. ROBERTSON</t>
+          <t>#27 M. MITEO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>20</v>
-      </c>
-      <c r="R23" t="n">
-        <v>22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>34</v>
-      </c>
-      <c r="T23" t="n">
-        <v>95</v>
-      </c>
-      <c r="U23" t="n">
-        <v>9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>13</v>
-      </c>
       <c r="W23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.672</v>
+        <v>0.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.292</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>286:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>146.72</v>
+        <v>7.2</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.432</v>
+        <v>0.75</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.481</v>
+        <v>0.806</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.832</v>
+        <v>1.389</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.245</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.243</v>
+        <v>0.318</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.008</v>
+        <v>0.106</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.098</v>
+        <v>0.112</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#30 K. ROBERTSON</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K24" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>370:07</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>183.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>0.854</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4164,19 +4164,19 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -4281,150 +4281,150 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>2259</v>
+        <v>2603</v>
       </c>
       <c r="D26" t="n">
-        <v>540</v>
+        <v>611</v>
       </c>
       <c r="E26" t="n">
-        <v>1004</v>
+        <v>1138</v>
       </c>
       <c r="F26" t="n">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="G26" t="n">
-        <v>749</v>
+        <v>864</v>
       </c>
       <c r="H26" t="n">
-        <v>447</v>
+        <v>511</v>
       </c>
       <c r="I26" t="n">
-        <v>627</v>
+        <v>702</v>
       </c>
       <c r="J26" t="n">
-        <v>436</v>
+        <v>491</v>
       </c>
       <c r="K26" t="n">
-        <v>633</v>
+        <v>735</v>
       </c>
       <c r="L26" t="n">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="M26" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="N26" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="Q26" t="n">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="R26" t="n">
-        <v>618</v>
+        <v>700</v>
       </c>
       <c r="S26" t="n">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="T26" t="n">
-        <v>2473</v>
+        <v>2831</v>
       </c>
       <c r="U26" t="n">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="V26" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="W26" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="X26" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="n">
-        <v>735</v>
+        <v>834</v>
       </c>
       <c r="Z26" t="n">
-        <v>1007</v>
+        <v>1129</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.73</v>
+        <v>0.739</v>
       </c>
       <c r="AB26" t="n">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="AC26" t="n">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.466</v>
+        <v>0.473</v>
       </c>
       <c r="AE26" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="AF26" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.309</v>
+        <v>0.307</v>
       </c>
       <c r="AH26" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AI26" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.338</v>
+        <v>0.357</v>
       </c>
       <c r="AK26" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="AL26" t="n">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.323</v>
+        <v>0.33</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2369.88</v>
+        <v>2702.88</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.517</v>
+        <v>0.522</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.953</v>
+        <v>0.963</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="AT26" t="n">
         <v>0.255</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.279</v>
+        <v>1.253</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="AX26" t="n">
         <v>0.138</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>2391</v>
+        <v>2740</v>
       </c>
       <c r="D27" t="n">
-        <v>536</v>
+        <v>647</v>
       </c>
       <c r="E27" t="n">
-        <v>971</v>
+        <v>1165</v>
       </c>
       <c r="F27" t="n">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="G27" t="n">
-        <v>722</v>
+        <v>802</v>
       </c>
       <c r="H27" t="n">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="I27" t="n">
-        <v>652</v>
+        <v>739</v>
       </c>
       <c r="J27" t="n">
-        <v>463</v>
+        <v>523</v>
       </c>
       <c r="K27" t="n">
-        <v>708</v>
+        <v>816</v>
       </c>
       <c r="L27" t="n">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="M27" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="N27" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="Q27" t="n">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="R27" t="n">
-        <v>639</v>
+        <v>715</v>
       </c>
       <c r="S27" t="n">
-        <v>614</v>
+        <v>696</v>
       </c>
       <c r="T27" t="n">
-        <v>2774</v>
+        <v>3176</v>
       </c>
       <c r="U27" t="n">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="V27" t="n">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="W27" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="X27" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="Y27" t="n">
-        <v>806</v>
+        <v>915</v>
       </c>
       <c r="Z27" t="n">
-        <v>1059</v>
+        <v>1215</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.761</v>
+        <v>0.753</v>
       </c>
       <c r="AB27" t="n">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="AC27" t="n">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="AD27" t="n">
         <v>0.455</v>
       </c>
       <c r="AE27" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AF27" t="n">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.373</v>
+        <v>0.382</v>
       </c>
       <c r="AH27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AI27" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="AK27" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="AL27" t="n">
-        <v>550</v>
+        <v>619</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.373</v>
+        <v>0.363</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2355.88</v>
+        <v>2712.16</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.556</v>
+        <v>0.554</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.015</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.301</v>
+        <v>0.285</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.231</v>
+        <v>1.245</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.062</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4656,40 +4656,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" t="n">
-        <v>0.478</v>
+        <v>0.52</v>
       </c>
       <c r="D29" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E29" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H29" t="n">
-        <v>0.217</v>
+        <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>0.435</v>
+        <v>0.48</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="L29" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4698,25 +4698,25 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0.261</v>
+        <v>0.24</v>
       </c>
       <c r="S29" t="n">
-        <v>0.348</v>
+        <v>0.36</v>
       </c>
       <c r="T29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U29" t="n">
-        <v>0.174</v>
+        <v>0.24</v>
       </c>
       <c r="V29" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4725,84 +4725,84 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.348</v>
+        <v>0.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.609</v>
+        <v>0.64</v>
       </c>
       <c r="AA29" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
         <v>0.571</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>02:28</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>0.583</v>
       </c>
       <c r="AP29" t="n">
         <v>0.375</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.444</v>
+        <v>0.489</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.821</v>
+        <v>0.91</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="AU29" t="n">
         <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="AY29" t="n">
         <v>0.003</v>
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>13.679</v>
+        <v>14.5</v>
       </c>
       <c r="D30" t="n">
-        <v>3.5</v>
+        <v>3.719</v>
       </c>
       <c r="E30" t="n">
-        <v>6.607</v>
+        <v>6.844</v>
       </c>
       <c r="F30" t="n">
-        <v>0.893</v>
+        <v>0.969</v>
       </c>
       <c r="G30" t="n">
-        <v>3.036</v>
+        <v>3.156</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>4.156</v>
       </c>
       <c r="I30" t="n">
-        <v>4.679</v>
+        <v>4.844</v>
       </c>
       <c r="J30" t="n">
-        <v>1.929</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5</v>
+        <v>1.531</v>
       </c>
       <c r="L30" t="n">
-        <v>0.607</v>
+        <v>0.531</v>
       </c>
       <c r="M30" t="n">
-        <v>0.929</v>
+        <v>0.906</v>
       </c>
       <c r="N30" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.143</v>
+        <v>1.125</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.143</v>
+        <v>1.125</v>
       </c>
       <c r="R30" t="n">
-        <v>2.714</v>
+        <v>2.719</v>
       </c>
       <c r="S30" t="n">
-        <v>3.464</v>
+        <v>3.625</v>
       </c>
       <c r="T30" t="n">
-        <v>358</v>
+        <v>437</v>
       </c>
       <c r="U30" t="n">
-        <v>1.607</v>
+        <v>1.875</v>
       </c>
       <c r="V30" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.107</v>
+        <v>1.188</v>
       </c>
       <c r="X30" t="n">
-        <v>0.714</v>
+        <v>0.781</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.5</v>
+        <v>5.781</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.607</v>
+        <v>6.906</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.832</v>
+        <v>0.837</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.214</v>
+        <v>1.281</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.464</v>
+        <v>2.531</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.493</v>
+        <v>0.506</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.786</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.214</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="AH30" t="n">
         <v>0.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.75</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.643</v>
+        <v>0.719</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.286</v>
+        <v>2.469</v>
       </c>
       <c r="AM30" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>13.256</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="AV30" t="n">
         <v>0.281</v>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21:49</t>
-        </is>
-      </c>
-      <c r="AO30" t="n">
-        <v>12.844</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.688</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0.279</v>
-      </c>
       <c r="AW30" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>2.286</v>
+        <v>2.344</v>
       </c>
       <c r="D31" t="n">
-        <v>0.321</v>
+        <v>0.312</v>
       </c>
       <c r="E31" t="n">
-        <v>0.75</v>
+        <v>0.781</v>
       </c>
       <c r="F31" t="n">
-        <v>0.393</v>
+        <v>0.438</v>
       </c>
       <c r="G31" t="n">
-        <v>1.357</v>
+        <v>1.281</v>
       </c>
       <c r="H31" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="I31" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="J31" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="K31" t="n">
         <v>0.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0.357</v>
+        <v>0.375</v>
       </c>
       <c r="M31" t="n">
-        <v>0.179</v>
+        <v>0.156</v>
       </c>
       <c r="N31" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="R31" t="n">
-        <v>0.929</v>
+        <v>0.875</v>
       </c>
       <c r="S31" t="n">
-        <v>0.571</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="T31" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="U31" t="n">
-        <v>0.607</v>
+        <v>0.531</v>
       </c>
       <c r="V31" t="n">
-        <v>0.357</v>
+        <v>0.375</v>
       </c>
       <c r="W31" t="n">
-        <v>0.107</v>
+        <v>0.188</v>
       </c>
       <c r="X31" t="n">
-        <v>0.036</v>
+        <v>0.062</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.643</v>
+        <v>0.594</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.929</v>
+        <v>0.844</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.321</v>
+        <v>0.281</v>
       </c>
       <c r="AD31" t="n">
         <v>0.333</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.214</v>
+        <v>0.281</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.167</v>
+        <v>0.111</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.321</v>
+        <v>0.344</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.857</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.375</v>
+        <v>0.423</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2.564</v>
+        <v>2.494</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.432</v>
+        <v>0.47</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.472</v>
+        <v>0.501</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.891</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.056</v>
+        <v>0.063</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.22</v>
+        <v>0.197</v>
       </c>
       <c r="AU31" t="n">
         <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.053</v>
+        <v>0.057</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="32">
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>5.071</v>
+        <v>4.531</v>
       </c>
       <c r="D32" t="n">
-        <v>1.393</v>
+        <v>1.219</v>
       </c>
       <c r="E32" t="n">
-        <v>3.036</v>
+        <v>2.75</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="G32" t="n">
-        <v>1.714</v>
+        <v>1.531</v>
       </c>
       <c r="H32" t="n">
-        <v>0.786</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.071</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>1.75</v>
+        <v>1.688</v>
       </c>
       <c r="K32" t="n">
-        <v>0.893</v>
+        <v>0.781</v>
       </c>
       <c r="L32" t="n">
-        <v>0.893</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="N32" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.929</v>
+        <v>0.875</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.929</v>
+        <v>0.875</v>
       </c>
       <c r="R32" t="n">
-        <v>1.857</v>
+        <v>1.719</v>
       </c>
       <c r="S32" t="n">
-        <v>1.071</v>
+        <v>0.969</v>
       </c>
       <c r="T32" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U32" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="V32" t="n">
-        <v>0.964</v>
+        <v>0.844</v>
       </c>
       <c r="W32" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="X32" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.107</v>
+        <v>1.906</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.678</v>
+        <v>0.656</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.25</v>
+        <v>1.125</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.75</v>
+        <v>0.656</v>
       </c>
       <c r="AG32" t="n">
         <v>0.333</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.4</v>
+        <v>0.455</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.357</v>
+        <v>0.312</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.357</v>
+        <v>1.188</v>
       </c>
       <c r="AM32" t="n">
         <v>0.263</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>6.15</v>
+        <v>5.569</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.825</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.151</v>
+        <v>0.157</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.165</v>
+        <v>0.161</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.885</v>
+        <v>1.929</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.221</v>
+        <v>0.217</v>
       </c>
       <c r="AW32" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AX32" t="n">
         <v>0.077</v>
       </c>
-      <c r="AX32" t="n">
-        <v>0.083</v>
-      </c>
       <c r="AY32" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>4.148</v>
+        <v>3.8</v>
       </c>
       <c r="D33" t="n">
-        <v>0.185</v>
+        <v>0.167</v>
       </c>
       <c r="E33" t="n">
-        <v>0.926</v>
+        <v>0.867</v>
       </c>
       <c r="F33" t="n">
-        <v>0.926</v>
+        <v>0.833</v>
       </c>
       <c r="G33" t="n">
-        <v>3.407</v>
+        <v>3.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="I33" t="n">
-        <v>1.481</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.481</v>
+        <v>3.333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.852</v>
+        <v>0.833</v>
       </c>
       <c r="L33" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0.889</v>
+        <v>0.867</v>
       </c>
       <c r="N33" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.593</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.593</v>
+        <v>1.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.667</v>
+        <v>1.767</v>
       </c>
       <c r="S33" t="n">
-        <v>2.704</v>
+        <v>2.567</v>
       </c>
       <c r="T33" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U33" t="n">
-        <v>0.926</v>
+        <v>0.9</v>
       </c>
       <c r="V33" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="W33" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="X33" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.074</v>
+        <v>1.033</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.778</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.604</v>
+        <v>0.608</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="AD33" t="n">
         <v>0.333</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.074</v>
+        <v>0.067</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.519</v>
+        <v>0.467</v>
       </c>
       <c r="AG33" t="n">
         <v>0.143</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.778</v>
+        <v>0.7</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.286</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.704</v>
+        <v>0.633</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.268</v>
+        <v>0.253</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>24:17</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.578</v>
+        <v>6.283</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.363</v>
+        <v>0.348</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.416</v>
+        <v>0.406</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.631</v>
+        <v>0.605</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.242</v>
+        <v>0.255</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.231</v>
+        <v>0.238</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.186</v>
+        <v>2.083</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AX33" t="n">
         <v>0.043</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>11.036</v>
+        <v>10.594</v>
       </c>
       <c r="D34" t="n">
         <v>1.75</v>
       </c>
       <c r="E34" t="n">
-        <v>2.964</v>
+        <v>2.938</v>
       </c>
       <c r="F34" t="n">
-        <v>1.714</v>
+        <v>1.625</v>
       </c>
       <c r="G34" t="n">
-        <v>4.893</v>
+        <v>4.688</v>
       </c>
       <c r="H34" t="n">
-        <v>2.393</v>
+        <v>2.219</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="J34" t="n">
         <v>2.25</v>
       </c>
       <c r="K34" t="n">
-        <v>3.036</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0.536</v>
+        <v>0.531</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.719</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.719</v>
       </c>
       <c r="R34" t="n">
-        <v>2.679</v>
+        <v>2.594</v>
       </c>
       <c r="S34" t="n">
-        <v>3.429</v>
+        <v>3.125</v>
       </c>
       <c r="T34" t="n">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="U34" t="n">
-        <v>1.571</v>
+        <v>1.375</v>
       </c>
       <c r="V34" t="n">
-        <v>1.464</v>
+        <v>1.344</v>
       </c>
       <c r="W34" t="n">
-        <v>0.286</v>
+        <v>0.312</v>
       </c>
       <c r="X34" t="n">
-        <v>0.179</v>
+        <v>0.188</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.5</v>
+        <v>3.312</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.357</v>
+        <v>4.062</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.803</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.964</v>
+        <v>0.969</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.519</v>
+        <v>0.548</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.643</v>
+        <v>0.656</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.222</v>
+        <v>0.19</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.857</v>
+        <v>0.781</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.429</v>
+        <v>1.375</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.036</v>
+        <v>3.906</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>27:19</t>
+          <t>27:31</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.927</v>
+        <v>10.554</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.601</v>
+        <v>0.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>1.004</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.305</v>
+        <v>0.291</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.286</v>
+        <v>1.309</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.19</v>
+        <v>0.183</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="35">
@@ -5750,13 +5750,13 @@
         <v>1.7</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.166</v>
+        <v>0.163</v>
       </c>
       <c r="AY35" t="n">
         <v>0.034</v>
@@ -5769,97 +5769,97 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C36" t="n">
-        <v>2.6</v>
+        <v>3.105</v>
       </c>
       <c r="D36" t="n">
-        <v>0.667</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1.467</v>
+        <v>1.368</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2</v>
+        <v>0.263</v>
       </c>
       <c r="G36" t="n">
-        <v>1.133</v>
+        <v>1.053</v>
       </c>
       <c r="H36" t="n">
-        <v>0.667</v>
+        <v>0.947</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.316</v>
       </c>
       <c r="J36" t="n">
-        <v>1.467</v>
+        <v>1.474</v>
       </c>
       <c r="K36" t="n">
-        <v>1.2</v>
+        <v>1.526</v>
       </c>
       <c r="L36" t="n">
-        <v>0.133</v>
+        <v>0.105</v>
       </c>
       <c r="M36" t="n">
-        <v>0.133</v>
+        <v>0.158</v>
       </c>
       <c r="N36" t="n">
-        <v>0.133</v>
+        <v>0.105</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.2</v>
+        <v>1.316</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.2</v>
+        <v>1.316</v>
       </c>
       <c r="R36" t="n">
-        <v>1.133</v>
+        <v>1.105</v>
       </c>
       <c r="S36" t="n">
-        <v>1.533</v>
+        <v>1.684</v>
       </c>
       <c r="T36" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.267</v>
+        <v>0.421</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>1.316</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.4</v>
+        <v>1.789</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.714</v>
+        <v>0.735</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.133</v>
+        <v>0.158</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.667</v>
+        <v>0.526</v>
       </c>
       <c r="AG36" t="n">
         <v>0.3</v>
@@ -5868,54 +5868,54 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AM36" t="n">
         <v>0.333</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>4.24</v>
+        <v>4.316</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.372</v>
+        <v>0.446</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.428</v>
+        <v>0.518</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.613</v>
+        <v>0.72</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.283</v>
+        <v>0.305</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.256</v>
+        <v>0.391</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.222</v>
+        <v>1.12</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.226</v>
+        <v>0.199</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.165</v>
+        <v>0.178</v>
       </c>
       <c r="AY36" t="n">
         <v>0.054</v>
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>8.964</v>
+        <v>9.468999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>2.357</v>
+        <v>2.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.786</v>
+        <v>3.969</v>
       </c>
       <c r="F37" t="n">
-        <v>1.143</v>
+        <v>1.219</v>
       </c>
       <c r="G37" t="n">
-        <v>2.607</v>
+        <v>2.906</v>
       </c>
       <c r="H37" t="n">
-        <v>0.821</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>1.107</v>
+        <v>1.062</v>
       </c>
       <c r="J37" t="n">
-        <v>1.179</v>
+        <v>1.156</v>
       </c>
       <c r="K37" t="n">
-        <v>3.357</v>
+        <v>3.812</v>
       </c>
       <c r="L37" t="n">
-        <v>1.179</v>
+        <v>1.188</v>
       </c>
       <c r="M37" t="n">
-        <v>0.857</v>
+        <v>0.844</v>
       </c>
       <c r="N37" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.857</v>
+        <v>0.781</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.857</v>
+        <v>0.781</v>
       </c>
       <c r="R37" t="n">
-        <v>2.607</v>
+        <v>2.656</v>
       </c>
       <c r="S37" t="n">
-        <v>1.179</v>
+        <v>1.188</v>
       </c>
       <c r="T37" t="n">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="U37" t="n">
-        <v>0.857</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="W37" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>1.812</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.321</v>
+        <v>2.375</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.754</v>
+        <v>0.763</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.964</v>
+        <v>1.031</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.571</v>
+        <v>1.688</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.614</v>
+        <v>0.611</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.464</v>
+        <v>0.469</v>
       </c>
       <c r="AF37" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.464</v>
+        <v>0.484</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.286</v>
+        <v>0.344</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.714</v>
+        <v>0.844</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.4</v>
+        <v>0.407</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.893</v>
+        <v>2.062</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.453</v>
+        <v>0.424</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>7.737</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.637</v>
+        <v>0.63</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.651</v>
+        <v>0.645</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.159</v>
+        <v>1.166</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.375</v>
+        <v>1.48</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.173</v>
+        <v>0.177</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.193</v>
+        <v>0.21</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C38" t="n">
-        <v>8.962</v>
+        <v>8.567</v>
       </c>
       <c r="D38" t="n">
-        <v>3.038</v>
+        <v>2.967</v>
       </c>
       <c r="E38" t="n">
-        <v>4.923</v>
+        <v>4.733</v>
       </c>
       <c r="F38" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="G38" t="n">
-        <v>2.038</v>
+        <v>1.9</v>
       </c>
       <c r="H38" t="n">
-        <v>1.269</v>
+        <v>1.233</v>
       </c>
       <c r="I38" t="n">
-        <v>1.923</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0.923</v>
+        <v>0.9</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.923</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="N38" t="n">
-        <v>0.654</v>
+        <v>0.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.962</v>
+        <v>0.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.962</v>
+        <v>0.9</v>
       </c>
       <c r="R38" t="n">
-        <v>2.923</v>
+        <v>2.8</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>1.967</v>
       </c>
       <c r="T38" t="n">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="U38" t="n">
-        <v>0.538</v>
+        <v>0.6</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W38" t="n">
-        <v>0.154</v>
+        <v>0.167</v>
       </c>
       <c r="X38" t="n">
-        <v>0.077</v>
+        <v>0.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.115</v>
+        <v>3.067</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.231</v>
+        <v>4.167</v>
       </c>
       <c r="AA38" t="n">
         <v>0.736</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.846</v>
+        <v>0.833</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.731</v>
+        <v>1.667</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.346</v>
+        <v>0.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.885</v>
+        <v>0.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="AL38" t="n">
-        <v>2</v>
+        <v>1.867</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.269</v>
+        <v>0.25</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>8.769</v>
+        <v>8.369</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.552</v>
+        <v>0.553</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.022</v>
+        <v>1.024</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="39">
@@ -6386,13 +6386,13 @@
         <v>0.625</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AY39" t="n">
         <v>0.008999999999999999</v>
@@ -6401,955 +6401,955 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#23 K. KUATH (Per Game)</t>
+          <t>#21 B. JEFFERSON (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>6.107</v>
+        <v>7.333</v>
       </c>
       <c r="D40" t="n">
-        <v>2.643</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>4.071</v>
+        <v>1.333</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="G40" t="n">
-        <v>0.036</v>
+        <v>5.667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.821</v>
+        <v>0.333</v>
       </c>
       <c r="I40" t="n">
-        <v>1.857</v>
+        <v>0.667</v>
       </c>
       <c r="J40" t="n">
-        <v>0.429</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1.821</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.321</v>
+        <v>0.667</v>
       </c>
       <c r="N40" t="n">
-        <v>1.821</v>
+        <v>0.667</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.714</v>
+        <v>1.333</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.714</v>
+        <v>1.333</v>
       </c>
       <c r="R40" t="n">
-        <v>1.786</v>
+        <v>2.333</v>
       </c>
       <c r="S40" t="n">
-        <v>1.714</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="U40" t="n">
-        <v>0.607</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>1.107</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="X40" t="n">
-        <v>0.179</v>
+        <v>0.333</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.571</v>
+        <v>0.333</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.929</v>
+        <v>0.667</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.655</v>
+        <v>0.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.857</v>
+        <v>0.333</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.036</v>
+        <v>4</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>5.639</v>
+        <v>8.627000000000001</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.643</v>
+        <v>0.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.62</v>
+        <v>0.503</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.083</v>
+        <v>0.85</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.127</v>
+        <v>0.155</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.2</v>
+        <v>0.048</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.187</v>
+        <v>0.219</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.156</v>
+        <v>0.064</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.017</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#24 B. ANGOLA (Per Game)</t>
+          <t>#23 K. KUATH (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C41" t="n">
-        <v>8.800000000000001</v>
+        <v>5.966</v>
       </c>
       <c r="D41" t="n">
-        <v>1.133</v>
+        <v>2.586</v>
       </c>
       <c r="E41" t="n">
-        <v>3.067</v>
+        <v>3.966</v>
       </c>
       <c r="F41" t="n">
-        <v>1.467</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4.6</v>
+        <v>0.034</v>
       </c>
       <c r="H41" t="n">
-        <v>2.133</v>
+        <v>0.793</v>
       </c>
       <c r="I41" t="n">
-        <v>3.067</v>
+        <v>1.793</v>
       </c>
       <c r="J41" t="n">
-        <v>1.8</v>
+        <v>0.448</v>
       </c>
       <c r="K41" t="n">
-        <v>1.533</v>
+        <v>1.759</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>1.172</v>
       </c>
       <c r="M41" t="n">
-        <v>0.867</v>
+        <v>0.345</v>
       </c>
       <c r="N41" t="n">
-        <v>0.333</v>
+        <v>1.759</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.533</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.533</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R41" t="n">
-        <v>2.533</v>
+        <v>1.793</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>1.655</v>
       </c>
       <c r="T41" t="n">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="U41" t="n">
-        <v>1.867</v>
+        <v>0.586</v>
       </c>
       <c r="V41" t="n">
-        <v>0.533</v>
+        <v>1.069</v>
       </c>
       <c r="W41" t="n">
-        <v>0.4</v>
+        <v>0.241</v>
       </c>
       <c r="X41" t="n">
-        <v>0.333</v>
+        <v>0.172</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.867</v>
+        <v>2.517</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.267</v>
+        <v>3.828</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.672</v>
+        <v>0.658</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2</v>
+        <v>0.828</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.067</v>
+        <v>1.793</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.188</v>
+        <v>0.462</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.2</v>
+        <v>0.034</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.8</v>
+        <v>0.138</v>
       </c>
       <c r="AG41" t="n">
         <v>0.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.9330000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.133</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.667</v>
+        <v>0.034</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.549</v>
+        <v>5.479</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.435</v>
+        <v>0.647</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.488</v>
+        <v>0.623</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.834</v>
+        <v>1.089</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.145</v>
+        <v>0.126</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.278</v>
+        <v>0.198</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.174</v>
+        <v>0.65</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.258</v>
+        <v>0.188</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.058</v>
+        <v>0.097</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.097</v>
+        <v>0.152</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#25 C. METU (Per Game)</t>
+          <t>#24 B. ANGOLA (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C42" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>3.167</v>
+        <v>1.133</v>
       </c>
       <c r="E42" t="n">
-        <v>6.333</v>
+        <v>3.067</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5</v>
+        <v>1.467</v>
       </c>
       <c r="G42" t="n">
-        <v>3.833</v>
+        <v>4.6</v>
       </c>
       <c r="H42" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>109</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.867</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AL42" t="n">
         <v>3.667</v>
       </c>
-      <c r="I42" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>86</v>
-      </c>
-      <c r="U42" t="n">
-        <v>3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.167</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>3</v>
-      </c>
       <c r="AM42" t="n">
-        <v>0.333</v>
+        <v>0.309</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>24:15</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>14.72</v>
+        <v>10.549</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.533</v>
+        <v>0.435</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.593</v>
+        <v>0.488</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.985</v>
+        <v>0.834</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.17</v>
+        <v>0.145</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.361</v>
+        <v>0.278</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.4</v>
+        <v>1.174</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.288</v>
+        <v>0.259</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.219</v>
+        <v>0.095</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.043</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#27 M. MITEO (Per Game)</t>
+          <t>#25 C. METU (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C43" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>133</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AK43" t="n">
         <v>1</v>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T43" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>01:48</t>
+          <t>25:48</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0.44</v>
+        <v>14.116</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.136</v>
+        <v>0.593</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.273</v>
+        <v>0.985</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.116</v>
+        <v>0.261</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.34</v>
+        <v>0.182</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#30 K. ROBERTSON (Per Game)</t>
+          <t>#27 M. MITEO (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>9.385</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1.692</v>
+        <v>0.6</v>
       </c>
       <c r="E44" t="n">
-        <v>4.308</v>
+        <v>0.8</v>
       </c>
       <c r="F44" t="n">
-        <v>1.308</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.154</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.077</v>
+        <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>2.923</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1.846</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.769</v>
+        <v>0.2</v>
       </c>
       <c r="L44" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0.231</v>
+        <v>0.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0.846</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.538</v>
+        <v>0.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.538</v>
+        <v>0.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.692</v>
+        <v>0.8</v>
       </c>
       <c r="S44" t="n">
-        <v>2.615</v>
+        <v>0.8</v>
       </c>
       <c r="T44" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="U44" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="V44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1</v>
       </c>
-      <c r="W44" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4.462</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AE44" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.385</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.077</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>3.692</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.292</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>02:09</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>11.286</v>
+        <v>1.44</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.432</v>
+        <v>0.75</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.481</v>
+        <v>0.806</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.832</v>
+        <v>1.389</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.245</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.243</v>
+        <v>0.318</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.008</v>
+        <v>0.106</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.098</v>
+        <v>0.112</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#30 K. ROBERTSON (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1.412</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1.471</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4.118</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.647</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1.706</v>
       </c>
       <c r="K45" t="n">
-        <v>1.679</v>
+        <v>1.471</v>
       </c>
       <c r="L45" t="n">
-        <v>1.214</v>
+        <v>0.118</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.821</v>
+        <v>1.529</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.529</v>
       </c>
       <c r="R45" t="n">
-        <v>0.143</v>
+        <v>1.765</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.353</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.706</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.941</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.176</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.529</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.176</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>3.529</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>10.812</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>0.854</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="46">
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.188</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,19 +7401,19 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
         <v>0</v>
@@ -7518,150 +7518,150 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>80.679</v>
+        <v>81.34399999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>19.286</v>
+        <v>19.094</v>
       </c>
       <c r="E47" t="n">
-        <v>35.857</v>
+        <v>35.562</v>
       </c>
       <c r="F47" t="n">
-        <v>8.714</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="H47" t="n">
-        <v>15.964</v>
+        <v>15.969</v>
       </c>
       <c r="I47" t="n">
-        <v>22.393</v>
+        <v>21.938</v>
       </c>
       <c r="J47" t="n">
-        <v>15.571</v>
+        <v>15.344</v>
       </c>
       <c r="K47" t="n">
-        <v>22.607</v>
+        <v>22.969</v>
       </c>
       <c r="L47" t="n">
-        <v>10.107</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>6.5</v>
+        <v>6.312</v>
       </c>
       <c r="N47" t="n">
-        <v>5.571</v>
+        <v>5.312</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>12.179</v>
+        <v>12.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.357</v>
+        <v>11.438</v>
       </c>
       <c r="R47" t="n">
-        <v>22.071</v>
+        <v>21.875</v>
       </c>
       <c r="S47" t="n">
-        <v>22.571</v>
+        <v>22.125</v>
       </c>
       <c r="T47" t="n">
-        <v>2473</v>
+        <v>2831</v>
       </c>
       <c r="U47" t="n">
-        <v>10.143</v>
+        <v>10.344</v>
       </c>
       <c r="V47" t="n">
-        <v>10.143</v>
+        <v>9.531000000000001</v>
       </c>
       <c r="W47" t="n">
-        <v>3.893</v>
+        <v>4.062</v>
       </c>
       <c r="X47" t="n">
-        <v>2.429</v>
+        <v>2.594</v>
       </c>
       <c r="Y47" t="n">
-        <v>26.25</v>
+        <v>26.062</v>
       </c>
       <c r="Z47" t="n">
-        <v>35.964</v>
+        <v>35.281</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.73</v>
+        <v>0.739</v>
       </c>
       <c r="AB47" t="n">
-        <v>6.286</v>
+        <v>6.219</v>
       </c>
       <c r="AC47" t="n">
-        <v>13.5</v>
+        <v>13.156</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.466</v>
+        <v>0.473</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.714</v>
+        <v>2.781</v>
       </c>
       <c r="AF47" t="n">
-        <v>8.786</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.309</v>
+        <v>0.307</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.893</v>
+        <v>2.062</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.607</v>
+        <v>5.781</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.338</v>
+        <v>0.357</v>
       </c>
       <c r="AK47" t="n">
-        <v>6.821</v>
+        <v>7</v>
       </c>
       <c r="AL47" t="n">
-        <v>21.143</v>
+        <v>21.219</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.323</v>
+        <v>0.33</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>200:53</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>84.639</v>
+        <v>84.465</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.517</v>
+        <v>0.522</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.953</v>
+        <v>0.963</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="AT47" t="n">
         <v>0.255</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.279</v>
+        <v>1.253</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="AX47" t="n">
         <v>0.138</v>
@@ -7677,153 +7677,153 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>85.393</v>
+        <v>85.625</v>
       </c>
       <c r="D48" t="n">
-        <v>19.143</v>
+        <v>20.219</v>
       </c>
       <c r="E48" t="n">
-        <v>34.679</v>
+        <v>36.406</v>
       </c>
       <c r="F48" t="n">
-        <v>9.643000000000001</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>25.786</v>
+        <v>25.062</v>
       </c>
       <c r="H48" t="n">
-        <v>18.179</v>
+        <v>17.531</v>
       </c>
       <c r="I48" t="n">
-        <v>23.286</v>
+        <v>23.094</v>
       </c>
       <c r="J48" t="n">
-        <v>16.536</v>
+        <v>16.344</v>
       </c>
       <c r="K48" t="n">
-        <v>25.286</v>
+        <v>25.5</v>
       </c>
       <c r="L48" t="n">
-        <v>10.214</v>
+        <v>10.438</v>
       </c>
       <c r="M48" t="n">
-        <v>7.214</v>
+        <v>7.344</v>
       </c>
       <c r="N48" t="n">
-        <v>5.536</v>
+        <v>5.312</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>13.429</v>
+        <v>13.125</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.321</v>
+        <v>12.094</v>
       </c>
       <c r="R48" t="n">
-        <v>22.821</v>
+        <v>22.344</v>
       </c>
       <c r="S48" t="n">
-        <v>21.929</v>
+        <v>21.75</v>
       </c>
       <c r="T48" t="n">
-        <v>2774</v>
+        <v>3176</v>
       </c>
       <c r="U48" t="n">
-        <v>10.786</v>
+        <v>10.75</v>
       </c>
       <c r="V48" t="n">
-        <v>9.643000000000001</v>
+        <v>9.593999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>4.5</v>
+        <v>4.469</v>
       </c>
       <c r="X48" t="n">
-        <v>3.071</v>
+        <v>3.031</v>
       </c>
       <c r="Y48" t="n">
-        <v>28.786</v>
+        <v>28.594</v>
       </c>
       <c r="Z48" t="n">
-        <v>37.821</v>
+        <v>37.969</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.761</v>
+        <v>0.753</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.643</v>
+        <v>5.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.393</v>
+        <v>12.625</v>
       </c>
       <c r="AD48" t="n">
         <v>0.455</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.893</v>
+        <v>3.406</v>
       </c>
       <c r="AF48" t="n">
-        <v>7.75</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.373</v>
+        <v>0.382</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.321</v>
+        <v>2.188</v>
       </c>
       <c r="AI48" t="n">
-        <v>6.143</v>
+        <v>5.719</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="AK48" t="n">
-        <v>7.321</v>
+        <v>7.031</v>
       </c>
       <c r="AL48" t="n">
-        <v>19.643</v>
+        <v>19.344</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.373</v>
+        <v>0.363</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>200:53</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>84.139</v>
+        <v>84.755</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.556</v>
+        <v>0.554</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.015</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.301</v>
+        <v>0.285</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.231</v>
+        <v>1.245</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.199</v>
+        <v>0.201</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Dreamland Gran Canaria.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Dreamland Gran Canaria.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2396.88</v>
+        <v>2553.84</v>
       </c>
       <c r="C2" t="n">
-        <v>2387.52</v>
+        <v>2545.72</v>
       </c>
       <c r="D2" t="n">
-        <v>109.0252647098244</v>
+        <v>108.5743915277407</v>
       </c>
       <c r="E2" t="n">
-        <v>114.7634365366573</v>
+        <v>115.1737033137973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5224775224775224</v>
+        <v>0.5220346929207689</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1450304860001184</v>
+        <v>0.1453993961403069</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2681704260651629</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2552447552447553</v>
+        <v>0.2517580872011252</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M2" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="N2" t="n">
-        <v>834</v>
+        <v>879</v>
       </c>
       <c r="O2" t="n">
-        <v>1129</v>
+        <v>1186</v>
       </c>
       <c r="P2" t="n">
-        <v>0.563936063936064</v>
+        <v>0.556024378809189</v>
       </c>
       <c r="Q2" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="R2" t="n">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2102897102897103</v>
+        <v>0.213314580403188</v>
       </c>
       <c r="T2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="U2" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1448551448551449</v>
+        <v>0.1420534458509142</v>
       </c>
       <c r="W2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X2" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0924075924075924</v>
+        <v>0.09423347398030943</v>
       </c>
       <c r="Z2" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AA2" t="n">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3391608391608392</v>
+        <v>0.3394280356305673</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7387068201948627</v>
+        <v>0.7411467116357504</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4726840855106889</v>
+        <v>0.4747252747252747</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3068965517241379</v>
+        <v>0.3135313531353136</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3567567567567568</v>
+        <v>0.3482587064676617</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3298969072164948</v>
+        <v>0.3273480662983426</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.477413640389725</v>
+        <v>1.482293423271501</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6137931034482759</v>
+        <v>0.6270627062706271</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.006944444444444</v>
+        <v>0.9956756756756757</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7880952380952381</v>
+        <v>0.8036529680365296</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9967320261437909</v>
+        <v>0.9781931464174455</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.566265060240964</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.252551020408163</v>
+        <v>1.22488038277512</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.107142857142857</v>
+        <v>5.102870813397129</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.35969387755102</v>
+        <v>6.327751196172249</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.9025</v>
+        <v>75.1129411764706</v>
       </c>
       <c r="C3" t="n">
-        <v>74.61</v>
+        <v>74.87411764705882</v>
       </c>
       <c r="D3" t="n">
-        <v>109.0252647098244</v>
+        <v>108.5743915277407</v>
       </c>
       <c r="E3" t="n">
-        <v>114.7634365366573</v>
+        <v>115.1737033137973</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5224775224775224</v>
+        <v>0.5220346929207689</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1450304860001184</v>
+        <v>0.1453993961403069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2681704260651629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2552447552447553</v>
+        <v>0.2517580872011252</v>
       </c>
       <c r="J3" t="n">
-        <v>10.34375</v>
+        <v>10.35294117647059</v>
       </c>
       <c r="K3" t="n">
-        <v>9.53125</v>
+        <v>9.235294117647058</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0625</v>
+        <v>3.911764705882353</v>
       </c>
       <c r="M3" t="n">
-        <v>11.4375</v>
+        <v>11.47058823529412</v>
       </c>
       <c r="N3" t="n">
-        <v>26.0625</v>
+        <v>25.85294117647059</v>
       </c>
       <c r="O3" t="n">
-        <v>35.28125</v>
+        <v>34.88235294117647</v>
       </c>
       <c r="P3" t="n">
-        <v>0.563936063936064</v>
+        <v>0.556024378809189</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.21875</v>
+        <v>6.352941176470588</v>
       </c>
       <c r="R3" t="n">
-        <v>13.15625</v>
+        <v>13.38235294117647</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2102897102897103</v>
+        <v>0.213314580403188</v>
       </c>
       <c r="T3" t="n">
-        <v>2.78125</v>
+        <v>2.794117647058823</v>
       </c>
       <c r="U3" t="n">
-        <v>9.0625</v>
+        <v>8.911764705882353</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1448551448551449</v>
+        <v>0.1420534458509142</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0625</v>
+        <v>2.058823529411764</v>
       </c>
       <c r="X3" t="n">
-        <v>5.78125</v>
+        <v>5.911764705882353</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0924075924075924</v>
+        <v>0.09423347398030943</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>6.970588235294118</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.21875</v>
+        <v>21.29411764705882</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3391608391608392</v>
+        <v>0.3394280356305673</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7387068201948627</v>
+        <v>0.7411467116357504</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4726840855106889</v>
+        <v>0.4747252747252747</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3068965517241379</v>
+        <v>0.3135313531353135</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3567567567567568</v>
+        <v>0.3482587064676617</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3298969072164948</v>
+        <v>0.3273480662983426</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.477413640389725</v>
+        <v>1.482293423271501</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6137931034482759</v>
+        <v>0.627062706270627</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.006944444444444</v>
+        <v>0.9956756756756757</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7880952380952381</v>
+        <v>0.8036529680365297</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9967320261437909</v>
+        <v>0.9781931464174454</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.566265060240964</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.252551020408163</v>
+        <v>1.22488038277512</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.107142857142857</v>
+        <v>5.102870813397129</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.35969387755102</v>
+        <v>6.327751196172248</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2378.16</v>
+        <v>2537.6</v>
       </c>
       <c r="C4" t="n">
-        <v>2387.52</v>
+        <v>2545.72</v>
       </c>
       <c r="D4" t="n">
-        <v>114.7634365366573</v>
+        <v>115.1737033137973</v>
       </c>
       <c r="E4" t="n">
-        <v>109.0252647098244</v>
+        <v>108.5743915277407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5538891713268937</v>
+        <v>0.5546837850689491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1548581204648693</v>
+        <v>0.1516305476701516</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3124415341440599</v>
+        <v>0.3092511013215859</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2852058973055414</v>
+        <v>0.284831193533048</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="N4" t="n">
-        <v>915</v>
+        <v>990</v>
       </c>
       <c r="O4" t="n">
-        <v>1215</v>
+        <v>1309</v>
       </c>
       <c r="P4" t="n">
-        <v>0.617691916624301</v>
+        <v>0.6224441274369947</v>
       </c>
       <c r="Q4" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="R4" t="n">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2053889171326894</v>
+        <v>0.2044698050404185</v>
       </c>
       <c r="T4" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="U4" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14489069649212</v>
+        <v>0.1421778411792677</v>
       </c>
       <c r="W4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X4" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09303507880020336</v>
+        <v>0.09272467902995721</v>
       </c>
       <c r="Z4" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AA4" t="n">
-        <v>619</v>
+        <v>660</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3146924250127097</v>
+        <v>0.3138373751783167</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.7563025210084033</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4554455445544555</v>
+        <v>0.4488372093023256</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3824561403508772</v>
+        <v>0.3879598662207358</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3825136612021858</v>
+        <v>0.3794871794871795</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3634894991922455</v>
+        <v>0.3590909090909091</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.506172839506173</v>
+        <v>1.512605042016807</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7649122807017544</v>
+        <v>0.7759197324414716</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.103491271820449</v>
+        <v>1.091228070175439</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8803827751196173</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9191616766467066</v>
+        <v>0.9373219373219374</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.474226804123711</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.245238095238095</v>
+        <v>1.262557077625571</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.683333333333334</v>
+        <v>4.801369863013699</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.928571428571429</v>
+        <v>6.063926940639269</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.31750000000001</v>
+        <v>74.63529411764706</v>
       </c>
       <c r="C5" t="n">
-        <v>74.61</v>
+        <v>74.87411764705882</v>
       </c>
       <c r="D5" t="n">
-        <v>114.7634365366573</v>
+        <v>115.1737033137973</v>
       </c>
       <c r="E5" t="n">
-        <v>109.0252647098244</v>
+        <v>108.5743915277407</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5538891713268937</v>
+        <v>0.5546837850689492</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1548581204648693</v>
+        <v>0.1516305476701516</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3124415341440599</v>
+        <v>0.3092511013215859</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2852058973055414</v>
+        <v>0.284831193533048</v>
       </c>
       <c r="J5" t="n">
-        <v>10.75</v>
+        <v>10.82352941176471</v>
       </c>
       <c r="K5" t="n">
-        <v>9.59375</v>
+        <v>9.676470588235293</v>
       </c>
       <c r="L5" t="n">
-        <v>4.46875</v>
+        <v>4.852941176470588</v>
       </c>
       <c r="M5" t="n">
-        <v>12.09375</v>
+        <v>11.91176470588235</v>
       </c>
       <c r="N5" t="n">
-        <v>28.59375</v>
+        <v>29.11764705882353</v>
       </c>
       <c r="O5" t="n">
-        <v>37.96875</v>
+        <v>38.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.617691916624301</v>
+        <v>0.6224441274369947</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>5.676470588235294</v>
       </c>
       <c r="R5" t="n">
-        <v>12.625</v>
+        <v>12.64705882352941</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2053889171326894</v>
+        <v>0.2044698050404185</v>
       </c>
       <c r="T5" t="n">
-        <v>3.40625</v>
+        <v>3.411764705882353</v>
       </c>
       <c r="U5" t="n">
-        <v>8.90625</v>
+        <v>8.794117647058824</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14489069649212</v>
+        <v>0.1421778411792677</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1875</v>
+        <v>2.176470588235294</v>
       </c>
       <c r="X5" t="n">
-        <v>5.71875</v>
+        <v>5.735294117647059</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09303507880020336</v>
+        <v>0.09272467902995721</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.03125</v>
+        <v>6.970588235294118</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.34375</v>
+        <v>19.41176470588235</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3146924250127097</v>
+        <v>0.3138373751783167</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.7563025210084033</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4554455445544555</v>
+        <v>0.4488372093023256</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3824561403508772</v>
+        <v>0.3879598662207357</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3825136612021858</v>
+        <v>0.3794871794871795</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3634894991922455</v>
+        <v>0.3590909090909091</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.506172839506173</v>
+        <v>1.512605042016807</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7649122807017544</v>
+        <v>0.7759197324414715</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.103491271820449</v>
+        <v>1.091228070175439</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8803827751196173</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9191616766467066</v>
+        <v>0.9373219373219372</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.474226804123711</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.245238095238095</v>
+        <v>1.262557077625571</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.683333333333334</v>
+        <v>4.801369863013698</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.928571428571429</v>
+        <v>6.06392694063927</v>
       </c>
     </row>
     <row r="7">
@@ -1562,7 +1562,7 @@
         <v>0.116</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="AX8" t="n">
         <v>0.041</v>
@@ -1578,64 +1578,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H9" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I9" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J9" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
         <v>17</v>
       </c>
       <c r="M9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="S9" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="T9" t="n">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="U9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V9" t="n">
         <v>32</v>
@@ -1647,84 +1647,84 @@
         <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="Z9" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.837</v>
+        <v>0.833</v>
       </c>
       <c r="AB9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.506</v>
+        <v>0.512</v>
       </c>
       <c r="AE9" t="n">
         <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="AH9" t="n">
         <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.291</v>
+        <v>0.299</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>721:46</t>
+          <t>777:25</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>424.2</v>
+        <v>456.28</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.517</v>
+        <v>0.523</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.598</v>
+        <v>0.599</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.094</v>
+        <v>1.085</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.416</v>
+        <v>0.401</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.778</v>
+        <v>1.581</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="AY9" t="n">
         <v>0.08500000000000001</v>
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" t="n">
         <v>13</v>
@@ -1764,10 +1764,10 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
@@ -1791,7 +1791,7 @@
         <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U10" t="n">
         <v>17</v>
@@ -1806,13 +1806,13 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.704</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
@@ -1845,33 +1845,33 @@
         <v>11</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.423</v>
+        <v>0.393</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>242:21</t>
+          <t>254:42</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>79.8</v>
+        <v>83.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.47</v>
+        <v>0.457</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.501</v>
+        <v>0.489</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.919</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.197</v>
+        <v>0.186</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
@@ -1880,13 +1880,13 @@
         <v>0.157</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.12</v>
+        <v>0.128</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="11">
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H11" t="n">
         <v>22</v>
@@ -1923,10 +1923,10 @@
         <v>54</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S11" t="n">
         <v>31</v>
       </c>
       <c r="T11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U11" t="n">
         <v>13</v>
@@ -1965,78 +1965,78 @@
         <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.656</v>
+        <v>0.651</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.389</v>
+        <v>0.405</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.455</v>
+        <v>0.429</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.263</v>
+        <v>0.256</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>392:29</t>
+          <t>405:17</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>178.2</v>
+        <v>187.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.483</v>
+        <v>0.48</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.929</v>
+        <v>1.862</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
         <v>0.076</v>
@@ -2045,7 +2045,7 @@
         <v>0.077</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="12">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F12" t="n">
         <v>26</v>
       </c>
-      <c r="F12" t="n">
-        <v>25</v>
-      </c>
       <c r="G12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>29</v>
@@ -2079,16 +2079,16 @@
         <v>42</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -2097,22 +2097,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="S12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="T12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="U12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -2133,13 +2133,13 @@
         <v>0.608</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2160,51 +2160,51 @@
         <v>0.286</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="n">
         <v>0.253</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>704:44</t>
+          <t>752:50</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>188.48</v>
+        <v>194.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.406</v>
+        <v>0.409</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.605</v>
+        <v>0.612</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.255</v>
+        <v>0.252</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.238</v>
+        <v>0.228</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.083</v>
+        <v>2.163</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.128</v>
+        <v>0.123</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="13">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="H13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I13" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K13" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="L13" t="n">
         <v>18</v>
       </c>
       <c r="M13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R13" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="T13" t="n">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="U13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W13" t="n">
         <v>10</v>
@@ -2283,87 +2283,87 @@
         <v>6</v>
       </c>
       <c r="Y13" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="Z13" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="AB13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.548</v>
+        <v>0.529</v>
       </c>
       <c r="AE13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.19</v>
+        <v>0.217</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>880:43</t>
+          <t>946:38</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>337.72</v>
+        <v>365.48</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.004</v>
+        <v>1.007</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.291</v>
+        <v>0.282</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.309</v>
+        <v>1.271</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="14">
@@ -2522,7 +2522,7 @@
         <v>0.163</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="15">
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -2550,22 +2550,22 @@
         <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -2574,22 +2574,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R15" t="n">
         <v>21</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.735</v>
+        <v>0.757</v>
       </c>
       <c r="AB15" t="n">
         <v>3</v>
@@ -2647,38 +2647,38 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>197:02</t>
+          <t>212:21</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>82</v>
+        <v>85.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.446</v>
+        <v>0.457</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.518</v>
+        <v>0.535</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.72</v>
+        <v>0.734</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.305</v>
+        <v>0.314</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.391</v>
+        <v>0.426</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.12</v>
+        <v>1.111</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.199</v>
+        <v>0.193</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
       <c r="AY15" t="n">
         <v>0.032</v>
@@ -2691,100 +2691,100 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
         <v>27</v>
       </c>
       <c r="N16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T16" t="n">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="U16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="W16" t="n">
+        <v>19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AE16" t="n">
         <v>16</v>
       </c>
-      <c r="X16" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>76</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>33</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>54</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>15</v>
-      </c>
       <c r="AF16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -2796,51 +2796,51 @@
         <v>0.407</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL16" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.424</v>
+        <v>0.414</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>699:52</t>
+          <t>741:15</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>259.96</v>
+        <v>276.72</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.63</v>
+        <v>0.622</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.645</v>
+        <v>0.641</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.166</v>
+        <v>1.156</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.118</v>
+        <v>0.129</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.48</v>
+        <v>1.407</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D17" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>43</v>
+      </c>
+      <c r="I17" t="n">
+        <v>66</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29</v>
+      </c>
+      <c r="K17" t="n">
+        <v>101</v>
+      </c>
+      <c r="L17" t="n">
         <v>57</v>
       </c>
-      <c r="H17" t="n">
-        <v>37</v>
-      </c>
-      <c r="I17" t="n">
-        <v>57</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>93</v>
-      </c>
-      <c r="L17" t="n">
-        <v>54</v>
-      </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="S17" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="T17" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="U17" t="n">
         <v>18</v>
       </c>
       <c r="V17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W17" t="n">
         <v>5</v>
@@ -2919,31 +2919,31 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="Z17" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="AA17" t="n">
         <v>0.736</v>
       </c>
       <c r="AB17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF17" t="n">
         <v>25</v>
       </c>
-      <c r="AC17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>24</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2955,48 +2955,48 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>629:53</t>
+          <t>677:52</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>251.08</v>
+        <v>272.04</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.553</v>
+        <v>0.554</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.573</v>
+        <v>0.576</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.024</v>
+        <v>1.029</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.186</v>
+        <v>0.201</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AY17" t="n">
         <v>0.034</v>
@@ -3158,7 +3158,7 @@
         <v>0.143</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="19">
@@ -3168,31 +3168,31 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" t="n">
         <v>3</v>
       </c>
-      <c r="C19" t="n">
-        <v>22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -3216,13 +3216,13 @@
         <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U19" t="n">
         <v>9</v>
@@ -3237,13 +3237,13 @@
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3255,69 +3255,69 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>56:21</t>
+          <t>79:21</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>25.88</v>
+        <v>34.76</v>
       </c>
       <c r="AP19" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.503</v>
+        <v>0.52</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.85</v>
+        <v>0.921</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.155</v>
+        <v>0.115</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.048</v>
+        <v>0.103</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.219</v>
+        <v>0.209</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.064</v>
+        <v>0.046</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="20">
@@ -3467,16 +3467,16 @@
         <v>0.65</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.188</v>
+        <v>0.187</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
       <c r="AX20" t="n">
         <v>0.152</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="21">
@@ -3635,7 +3635,7 @@
         <v>0.095</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="22">
@@ -3645,64 +3645,64 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>169</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38</v>
+      </c>
+      <c r="E22" t="n">
+        <v>76</v>
+      </c>
+      <c r="F22" t="n">
+        <v>19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52</v>
+      </c>
+      <c r="H22" t="n">
+        <v>36</v>
+      </c>
+      <c r="I22" t="n">
+        <v>45</v>
+      </c>
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" t="n">
-        <v>139</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="K22" t="n">
+        <v>46</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>28</v>
       </c>
-      <c r="E22" t="n">
-        <v>59</v>
-      </c>
-      <c r="F22" t="n">
-        <v>17</v>
-      </c>
-      <c r="G22" t="n">
-        <v>41</v>
-      </c>
-      <c r="H22" t="n">
-        <v>32</v>
-      </c>
-      <c r="I22" t="n">
-        <v>39</v>
-      </c>
-      <c r="J22" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>39</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>24</v>
-      </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S22" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="T22" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="U22" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V22" t="n">
         <v>9</v>
@@ -3714,87 +3714,87 @@
         <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Z22" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.86</v>
+        <v>0.839</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AC22" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.409</v>
+        <v>0.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.308</v>
+        <v>0.323</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.538</v>
+        <v>0.438</v>
       </c>
       <c r="AK22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL22" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>314:52</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AU22" t="n">
         <v>0.357</v>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>258:04</t>
-        </is>
-      </c>
-      <c r="AO22" t="n">
-        <v>141.16</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AV22" t="n">
-        <v>0.261</v>
+        <v>0.266</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.182</v>
+        <v>0.176</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="23">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
         <v>10</v>
@@ -3963,22 +3963,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C24" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D24" t="n">
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H24" t="n">
         <v>34</v>
@@ -3990,7 +3990,7 @@
         <v>29</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -4005,19 +4005,19 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R24" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S24" t="n">
         <v>40</v>
       </c>
       <c r="T24" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -4035,34 +4035,34 @@
         <v>46</v>
       </c>
       <c r="Z24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="AB24" t="n">
         <v>7</v>
       </c>
       <c r="AC24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AE24" t="n">
         <v>5</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.5</v>
@@ -4078,41 +4078,41 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>370:07</t>
+          <t>390:59</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>183.8</v>
+        <v>189.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.446</v>
+        <v>0.441</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.497</v>
+        <v>0.491</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.854</v>
+        <v>0.843</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.246</v>
+        <v>0.238</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.115</v>
+        <v>1.074</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="AW24" t="n">
         <v>0.006</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4281,126 +4281,126 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>2603</v>
+        <v>2764</v>
       </c>
       <c r="D26" t="n">
-        <v>611</v>
+        <v>653</v>
       </c>
       <c r="E26" t="n">
-        <v>1138</v>
+        <v>1208</v>
       </c>
       <c r="F26" t="n">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="G26" t="n">
-        <v>864</v>
+        <v>925</v>
       </c>
       <c r="H26" t="n">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="I26" t="n">
-        <v>702</v>
+        <v>736</v>
       </c>
       <c r="J26" t="n">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="K26" t="n">
-        <v>735</v>
+        <v>784</v>
       </c>
       <c r="L26" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="M26" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N26" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="Q26" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="R26" t="n">
-        <v>700</v>
+        <v>744</v>
       </c>
       <c r="S26" t="n">
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="T26" t="n">
-        <v>2831</v>
+        <v>2984</v>
       </c>
       <c r="U26" t="n">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="V26" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="W26" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="X26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y26" t="n">
-        <v>834</v>
+        <v>879</v>
       </c>
       <c r="Z26" t="n">
-        <v>1129</v>
+        <v>1186</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="AB26" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="AC26" t="n">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="AE26" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.307</v>
+        <v>0.314</v>
       </c>
       <c r="AH26" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AI26" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.357</v>
+        <v>0.348</v>
       </c>
       <c r="AK26" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="n">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2702.88</v>
+        <v>2874.84</v>
       </c>
       <c r="AP26" t="n">
         <v>0.522</v>
@@ -4409,22 +4409,22 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.963</v>
+        <v>0.961</v>
       </c>
       <c r="AS26" t="n">
         <v>0.145</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.255</v>
+        <v>0.252</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.253</v>
+        <v>1.225</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="AX26" t="n">
         <v>0.138</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2740</v>
+        <v>2932</v>
       </c>
       <c r="D27" t="n">
-        <v>647</v>
+        <v>700</v>
       </c>
       <c r="E27" t="n">
-        <v>1165</v>
+        <v>1248</v>
       </c>
       <c r="F27" t="n">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="G27" t="n">
-        <v>802</v>
+        <v>855</v>
       </c>
       <c r="H27" t="n">
-        <v>561</v>
+        <v>599</v>
       </c>
       <c r="I27" t="n">
+        <v>790</v>
+      </c>
+      <c r="J27" t="n">
+        <v>553</v>
+      </c>
+      <c r="K27" t="n">
+        <v>876</v>
+      </c>
+      <c r="L27" t="n">
+        <v>351</v>
+      </c>
+      <c r="M27" t="n">
+        <v>251</v>
+      </c>
+      <c r="N27" t="n">
+        <v>176</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>405</v>
+      </c>
+      <c r="R27" t="n">
+        <v>755</v>
+      </c>
+      <c r="S27" t="n">
         <v>739</v>
       </c>
-      <c r="J27" t="n">
-        <v>523</v>
-      </c>
-      <c r="K27" t="n">
-        <v>816</v>
-      </c>
-      <c r="L27" t="n">
-        <v>334</v>
-      </c>
-      <c r="M27" t="n">
-        <v>235</v>
-      </c>
-      <c r="N27" t="n">
-        <v>170</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>387</v>
-      </c>
-      <c r="R27" t="n">
-        <v>715</v>
-      </c>
-      <c r="S27" t="n">
-        <v>696</v>
-      </c>
       <c r="T27" t="n">
-        <v>3176</v>
+        <v>3402</v>
       </c>
       <c r="U27" t="n">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="V27" t="n">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="W27" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="X27" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="Y27" t="n">
-        <v>915</v>
+        <v>990</v>
       </c>
       <c r="Z27" t="n">
-        <v>1215</v>
+        <v>1309</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="AB27" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AC27" t="n">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.455</v>
+        <v>0.449</v>
       </c>
       <c r="AE27" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="AF27" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="AH27" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.383</v>
+        <v>0.379</v>
       </c>
       <c r="AK27" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AL27" t="n">
-        <v>619</v>
+        <v>660</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2712.16</v>
+        <v>2888.6</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.554</v>
+        <v>0.555</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.598</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>1.015</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AT27" t="n">
         <v>0.285</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.245</v>
+        <v>1.263</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.062</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
         <v>0.116</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="AX29" t="n">
         <v>0.041</v>
@@ -4815,153 +4815,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>14.5</v>
+        <v>14.559</v>
       </c>
       <c r="D30" t="n">
-        <v>3.719</v>
+        <v>3.765</v>
       </c>
       <c r="E30" t="n">
-        <v>6.844</v>
+        <v>6.794</v>
       </c>
       <c r="F30" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.156</v>
+        <v>3.265</v>
       </c>
       <c r="H30" t="n">
-        <v>4.156</v>
+        <v>4.029</v>
       </c>
       <c r="I30" t="n">
-        <v>4.844</v>
+        <v>4.765</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>1.531</v>
+        <v>1.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0.906</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.125</v>
+        <v>1.265</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.125</v>
+        <v>1.265</v>
       </c>
       <c r="R30" t="n">
-        <v>2.719</v>
+        <v>2.735</v>
       </c>
       <c r="S30" t="n">
-        <v>3.625</v>
+        <v>3.559</v>
       </c>
       <c r="T30" t="n">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="U30" t="n">
-        <v>1.875</v>
+        <v>1.912</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.188</v>
+        <v>1.118</v>
       </c>
       <c r="X30" t="n">
-        <v>0.781</v>
+        <v>0.735</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.781</v>
+        <v>5.735</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.906</v>
+        <v>6.882</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.837</v>
+        <v>0.833</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.531</v>
+        <v>2.529</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.506</v>
+        <v>0.512</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.147</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.719</v>
+        <v>0.765</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.469</v>
+        <v>2.559</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.291</v>
+        <v>0.299</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>13.256</v>
+        <v>13.42</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.517</v>
+        <v>0.523</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.598</v>
+        <v>0.599</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.094</v>
+        <v>1.085</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.416</v>
+        <v>0.401</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.778</v>
+        <v>1.581</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="AY30" t="n">
         <v>0.08500000000000001</v>
@@ -4974,141 +4974,141 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>2.344</v>
+        <v>2.265</v>
       </c>
       <c r="D31" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="E31" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="F31" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="G31" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="H31" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="I31" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="J31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="K31" t="n">
-        <v>0.75</v>
+        <v>0.794</v>
       </c>
       <c r="L31" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="M31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="N31" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="R31" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="T31" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U31" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="W31" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="X31" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.704</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="AD31" t="n">
         <v>0.333</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="AG31" t="n">
         <v>0.111</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.423</v>
+        <v>0.393</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2.494</v>
+        <v>2.465</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.47</v>
+        <v>0.457</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.501</v>
+        <v>0.489</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.919</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.197</v>
+        <v>0.186</v>
       </c>
       <c r="AU31" t="n">
         <v>1</v>
@@ -5117,13 +5117,13 @@
         <v>0.157</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.12</v>
+        <v>0.128</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="32">
@@ -5133,147 +5133,147 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>4.531</v>
+        <v>4.471</v>
       </c>
       <c r="D32" t="n">
-        <v>1.219</v>
+        <v>1.206</v>
       </c>
       <c r="E32" t="n">
-        <v>2.75</v>
+        <v>2.706</v>
       </c>
       <c r="F32" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="G32" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="J32" t="n">
-        <v>1.688</v>
+        <v>1.588</v>
       </c>
       <c r="K32" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="L32" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="T32" t="n">
+        <v>128</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>5.506</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AR32" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="M32" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="T32" t="n">
-        <v>127</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.906</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>5.569</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0.8139999999999999</v>
-      </c>
       <c r="AS32" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.929</v>
+        <v>1.862</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="AW32" t="n">
         <v>0.076</v>
@@ -5282,7 +5282,7 @@
         <v>0.077</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>3.8</v>
+        <v>3.719</v>
       </c>
       <c r="D33" t="n">
-        <v>0.167</v>
+        <v>0.188</v>
       </c>
       <c r="E33" t="n">
-        <v>0.867</v>
+        <v>0.844</v>
       </c>
       <c r="F33" t="n">
-        <v>0.833</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>3.2</v>
+        <v>3.125</v>
       </c>
       <c r="H33" t="n">
-        <v>0.967</v>
+        <v>0.906</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1.312</v>
       </c>
       <c r="J33" t="n">
-        <v>3.333</v>
+        <v>3.312</v>
       </c>
       <c r="K33" t="n">
-        <v>0.833</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="M33" t="n">
-        <v>0.867</v>
+        <v>0.844</v>
       </c>
       <c r="N33" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.6</v>
+        <v>1.531</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.6</v>
+        <v>1.531</v>
       </c>
       <c r="R33" t="n">
-        <v>1.767</v>
+        <v>1.812</v>
       </c>
       <c r="S33" t="n">
-        <v>2.567</v>
+        <v>2.594</v>
       </c>
       <c r="T33" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9</v>
+        <v>0.906</v>
       </c>
       <c r="V33" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.033</v>
+        <v>0.969</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.7</v>
+        <v>1.594</v>
       </c>
       <c r="AA33" t="n">
         <v>0.608</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.033</v>
+        <v>0.062</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="AG33" t="n">
         <v>0.143</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.7</v>
+        <v>0.656</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.286</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.633</v>
+        <v>0.625</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.5</v>
+        <v>2.469</v>
       </c>
       <c r="AM33" t="n">
         <v>0.253</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.283</v>
+        <v>6.077</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.406</v>
+        <v>0.409</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.605</v>
+        <v>0.612</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.255</v>
+        <v>0.252</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.238</v>
+        <v>0.228</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.083</v>
+        <v>2.163</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.128</v>
+        <v>0.123</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>10.594</v>
+        <v>10.824</v>
       </c>
       <c r="D34" t="n">
-        <v>1.75</v>
+        <v>1.794</v>
       </c>
       <c r="E34" t="n">
-        <v>2.938</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.625</v>
+        <v>1.676</v>
       </c>
       <c r="G34" t="n">
-        <v>4.688</v>
+        <v>4.824</v>
       </c>
       <c r="H34" t="n">
-        <v>2.219</v>
+        <v>2.206</v>
       </c>
       <c r="I34" t="n">
-        <v>2.75</v>
+        <v>2.706</v>
       </c>
       <c r="J34" t="n">
-        <v>2.25</v>
+        <v>2.206</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>3.088</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="M34" t="n">
-        <v>1.25</v>
+        <v>1.235</v>
       </c>
       <c r="N34" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.719</v>
+        <v>1.735</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.719</v>
+        <v>1.735</v>
       </c>
       <c r="R34" t="n">
-        <v>2.594</v>
+        <v>2.618</v>
       </c>
       <c r="S34" t="n">
-        <v>3.125</v>
+        <v>3.206</v>
       </c>
       <c r="T34" t="n">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="U34" t="n">
-        <v>1.375</v>
+        <v>1.412</v>
       </c>
       <c r="V34" t="n">
-        <v>1.344</v>
+        <v>1.353</v>
       </c>
       <c r="W34" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="X34" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.312</v>
+        <v>3.324</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.062</v>
+        <v>4.029</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.548</v>
+        <v>0.529</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.656</v>
+        <v>0.676</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.19</v>
+        <v>0.217</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.781</v>
+        <v>0.824</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.375</v>
+        <v>1.412</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.906</v>
+        <v>4</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>27:31</t>
+          <t>27:50</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.554</v>
+        <v>10.749</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.004</v>
+        <v>1.007</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.291</v>
+        <v>0.282</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.309</v>
+        <v>1.271</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="35">
@@ -5769,97 +5769,97 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C36" t="n">
-        <v>3.105</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="E36" t="n">
-        <v>1.368</v>
+        <v>1.286</v>
       </c>
       <c r="F36" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="G36" t="n">
-        <v>1.053</v>
+        <v>0.952</v>
       </c>
       <c r="H36" t="n">
-        <v>0.947</v>
+        <v>0.952</v>
       </c>
       <c r="I36" t="n">
-        <v>1.316</v>
+        <v>1.286</v>
       </c>
       <c r="J36" t="n">
-        <v>1.474</v>
+        <v>1.429</v>
       </c>
       <c r="K36" t="n">
-        <v>1.526</v>
+        <v>1.524</v>
       </c>
       <c r="L36" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="M36" t="n">
-        <v>0.158</v>
+        <v>0.19</v>
       </c>
       <c r="N36" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.316</v>
+        <v>1.286</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.316</v>
+        <v>1.286</v>
       </c>
       <c r="R36" t="n">
-        <v>1.105</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>1.684</v>
+        <v>1.571</v>
       </c>
       <c r="T36" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="U36" t="n">
-        <v>0.158</v>
+        <v>0.238</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.421</v>
+        <v>0.381</v>
       </c>
       <c r="X36" t="n">
-        <v>0.316</v>
+        <v>0.286</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.316</v>
+        <v>1.333</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.789</v>
+        <v>1.762</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.735</v>
+        <v>0.757</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.158</v>
+        <v>0.143</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.368</v>
+        <v>0.333</v>
       </c>
       <c r="AD36" t="n">
         <v>0.429</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.158</v>
+        <v>0.143</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.526</v>
+        <v>0.476</v>
       </c>
       <c r="AG36" t="n">
         <v>0.3</v>
@@ -5868,57 +5868,57 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.789</v>
+        <v>0.714</v>
       </c>
       <c r="AM36" t="n">
         <v>0.333</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>4.316</v>
+        <v>4.09</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.446</v>
+        <v>0.457</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.518</v>
+        <v>0.535</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.72</v>
+        <v>0.734</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.305</v>
+        <v>0.314</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.391</v>
+        <v>0.426</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.12</v>
+        <v>1.111</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.199</v>
+        <v>0.193</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>9.468999999999999</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="D37" t="n">
         <v>2.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.969</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.219</v>
+        <v>1.176</v>
       </c>
       <c r="G37" t="n">
-        <v>2.906</v>
+        <v>2.853</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="I37" t="n">
-        <v>1.062</v>
+        <v>1.118</v>
       </c>
       <c r="J37" t="n">
-        <v>1.156</v>
+        <v>1.118</v>
       </c>
       <c r="K37" t="n">
-        <v>3.812</v>
+        <v>3.824</v>
       </c>
       <c r="L37" t="n">
-        <v>1.188</v>
+        <v>1.294</v>
       </c>
       <c r="M37" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="N37" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="R37" t="n">
-        <v>2.656</v>
+        <v>2.647</v>
       </c>
       <c r="S37" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="T37" t="n">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="V37" t="n">
-        <v>1.125</v>
+        <v>1.176</v>
       </c>
       <c r="W37" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.412</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.5</v>
       </c>
-      <c r="X37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.812</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.031</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.688</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.484</v>
-      </c>
       <c r="AH37" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.407</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.062</v>
+        <v>2.059</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.424</v>
+        <v>0.414</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>8.124000000000001</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.63</v>
+        <v>0.622</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.645</v>
+        <v>0.641</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.166</v>
+        <v>1.156</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.118</v>
+        <v>0.129</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.48</v>
+        <v>1.407</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>8.567</v>
+        <v>8.75</v>
       </c>
       <c r="D38" t="n">
-        <v>2.967</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>4.733</v>
+        <v>4.812</v>
       </c>
       <c r="F38" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="G38" t="n">
-        <v>1.9</v>
+        <v>1.875</v>
       </c>
       <c r="H38" t="n">
-        <v>1.233</v>
+        <v>1.344</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2.062</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9</v>
+        <v>0.906</v>
       </c>
       <c r="K38" t="n">
-        <v>3.1</v>
+        <v>3.156</v>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>1.781</v>
       </c>
       <c r="M38" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="N38" t="n">
-        <v>0.7</v>
+        <v>0.719</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9</v>
+        <v>0.906</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9</v>
+        <v>0.906</v>
       </c>
       <c r="R38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S38" t="n">
-        <v>1.967</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="U38" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="V38" t="n">
-        <v>1.9</v>
+        <v>1.844</v>
       </c>
       <c r="W38" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="X38" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.067</v>
+        <v>3.219</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.167</v>
+        <v>4.375</v>
       </c>
       <c r="AA38" t="n">
         <v>0.736</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.833</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.667</v>
+        <v>1.719</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.5</v>
+        <v>0.473</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.3</v>
+        <v>0.312</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.8</v>
+        <v>0.781</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.867</v>
+        <v>1.844</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>8.369</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.553</v>
+        <v>0.554</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.573</v>
+        <v>0.576</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.024</v>
+        <v>1.029</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.186</v>
+        <v>0.201</v>
       </c>
       <c r="AU38" t="n">
         <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="39">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>7.333</v>
+        <v>6.4</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>2.333</v>
+        <v>1.8</v>
       </c>
       <c r="G40" t="n">
-        <v>5.667</v>
+        <v>4.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="I40" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.333</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="X40" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL40" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.5</v>
+        <v>0.437</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>8.627000000000001</v>
+        <v>6.952</v>
       </c>
       <c r="AP40" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.503</v>
+        <v>0.52</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.85</v>
+        <v>0.921</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.155</v>
+        <v>0.115</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.048</v>
+        <v>0.103</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.219</v>
+        <v>0.209</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.064</v>
+        <v>0.046</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="41">
@@ -6704,16 +6704,16 @@
         <v>0.65</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.188</v>
+        <v>0.187</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
       <c r="AX41" t="n">
         <v>0.152</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="42">
@@ -6882,156 +6882,156 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>13.9</v>
+        <v>14.083</v>
       </c>
       <c r="D43" t="n">
-        <v>2.8</v>
+        <v>3.167</v>
       </c>
       <c r="E43" t="n">
-        <v>5.9</v>
+        <v>6.333</v>
       </c>
       <c r="F43" t="n">
-        <v>1.7</v>
+        <v>1.583</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>4.333</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="K43" t="n">
-        <v>3.9</v>
+        <v>3.833</v>
       </c>
       <c r="L43" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="M43" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="T43" t="n">
+        <v>159</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="X43" t="n">
         <v>0.5</v>
       </c>
-      <c r="N43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T43" t="n">
-        <v>133</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.6</v>
-      </c>
       <c r="Y43" t="n">
-        <v>4.3</v>
+        <v>3.917</v>
       </c>
       <c r="Z43" t="n">
-        <v>5</v>
+        <v>4.667</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.86</v>
+        <v>0.839</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.9</v>
+        <v>1.417</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.2</v>
+        <v>2.833</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.409</v>
+        <v>0.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.6</v>
+        <v>2.583</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.308</v>
+        <v>0.323</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.7</v>
+        <v>0.583</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.3</v>
+        <v>1.333</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.538</v>
+        <v>0.438</v>
       </c>
       <c r="AK43" t="n">
         <v>1</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AM43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>26:14</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AU43" t="n">
         <v>0.357</v>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>25:48</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>14.116</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AV43" t="n">
-        <v>0.261</v>
+        <v>0.266</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.182</v>
+        <v>0.176</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="44">
@@ -7041,16 +7041,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1.429</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -7059,22 +7059,22 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -7083,25 +7083,25 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="R44" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="S44" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="T44" t="n">
         <v>10</v>
       </c>
       <c r="U44" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="V44" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -7110,19 +7110,19 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0.857</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.6</v>
+        <v>1.143</v>
       </c>
       <c r="AA44" t="n">
         <v>0.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AD44" t="n">
         <v>1</v>
@@ -7156,11 +7156,11 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>02:09</t>
+          <t>01:32</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.44</v>
+        <v>1.029</v>
       </c>
       <c r="AP44" t="n">
         <v>0.75</v>
@@ -7200,156 +7200,156 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>9.234999999999999</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>1.412</v>
+        <v>1.263</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>3.737</v>
       </c>
       <c r="F45" t="n">
-        <v>1.471</v>
+        <v>1.368</v>
       </c>
       <c r="G45" t="n">
-        <v>4.118</v>
+        <v>3.789</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1.789</v>
       </c>
       <c r="I45" t="n">
-        <v>2.647</v>
+        <v>2.368</v>
       </c>
       <c r="J45" t="n">
-        <v>1.706</v>
+        <v>1.526</v>
       </c>
       <c r="K45" t="n">
-        <v>1.471</v>
+        <v>1.368</v>
       </c>
       <c r="L45" t="n">
-        <v>0.118</v>
+        <v>0.105</v>
       </c>
       <c r="M45" t="n">
-        <v>0.235</v>
+        <v>0.211</v>
       </c>
       <c r="N45" t="n">
-        <v>0.706</v>
+        <v>0.632</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.529</v>
+        <v>1.421</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.529</v>
+        <v>1.421</v>
       </c>
       <c r="R45" t="n">
-        <v>1.765</v>
+        <v>1.842</v>
       </c>
       <c r="S45" t="n">
-        <v>2.353</v>
+        <v>2.105</v>
       </c>
       <c r="T45" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="U45" t="n">
-        <v>0.765</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="V45" t="n">
-        <v>0.765</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>0.412</v>
+        <v>0.368</v>
       </c>
       <c r="X45" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.706</v>
+        <v>2.421</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.941</v>
+        <v>3.579</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.412</v>
+        <v>0.368</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.176</v>
+        <v>1.105</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.294</v>
+        <v>0.263</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.529</v>
+        <v>1.421</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.294</v>
+        <v>0.316</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.588</v>
+        <v>0.632</v>
       </c>
       <c r="AJ45" t="n">
         <v>0.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.176</v>
+        <v>1.053</v>
       </c>
       <c r="AL45" t="n">
-        <v>3.529</v>
+        <v>3.158</v>
       </c>
       <c r="AM45" t="n">
         <v>0.333</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>10.812</v>
+        <v>9.989000000000001</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.446</v>
+        <v>0.441</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.497</v>
+        <v>0.491</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.854</v>
+        <v>0.843</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.246</v>
+        <v>0.238</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.115</v>
+        <v>1.074</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="AW45" t="n">
         <v>0.006</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.067</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="46">
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.688</v>
+        <v>1.765</v>
       </c>
       <c r="L46" t="n">
-        <v>1.188</v>
+        <v>1.176</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7518,126 +7518,126 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>81.34399999999999</v>
+        <v>81.294</v>
       </c>
       <c r="D47" t="n">
-        <v>19.094</v>
+        <v>19.206</v>
       </c>
       <c r="E47" t="n">
-        <v>35.562</v>
+        <v>35.529</v>
       </c>
       <c r="F47" t="n">
-        <v>9.061999999999999</v>
+        <v>9.029</v>
       </c>
       <c r="G47" t="n">
-        <v>27</v>
+        <v>27.206</v>
       </c>
       <c r="H47" t="n">
-        <v>15.969</v>
+        <v>15.794</v>
       </c>
       <c r="I47" t="n">
-        <v>21.938</v>
+        <v>21.647</v>
       </c>
       <c r="J47" t="n">
-        <v>15.344</v>
+        <v>15.059</v>
       </c>
       <c r="K47" t="n">
-        <v>22.969</v>
+        <v>23.059</v>
       </c>
       <c r="L47" t="n">
-        <v>9.561999999999999</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>6.312</v>
+        <v>6.265</v>
       </c>
       <c r="N47" t="n">
-        <v>5.312</v>
+        <v>5.176</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>12.25</v>
+        <v>12.294</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.438</v>
+        <v>11.471</v>
       </c>
       <c r="R47" t="n">
-        <v>21.875</v>
+        <v>21.882</v>
       </c>
       <c r="S47" t="n">
-        <v>22.125</v>
+        <v>22</v>
       </c>
       <c r="T47" t="n">
-        <v>2831</v>
+        <v>2984</v>
       </c>
       <c r="U47" t="n">
-        <v>10.344</v>
+        <v>10.353</v>
       </c>
       <c r="V47" t="n">
-        <v>9.531000000000001</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>4.062</v>
+        <v>3.912</v>
       </c>
       <c r="X47" t="n">
-        <v>2.594</v>
+        <v>2.471</v>
       </c>
       <c r="Y47" t="n">
-        <v>26.062</v>
+        <v>25.853</v>
       </c>
       <c r="Z47" t="n">
-        <v>35.281</v>
+        <v>34.882</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="AB47" t="n">
-        <v>6.219</v>
+        <v>6.353</v>
       </c>
       <c r="AC47" t="n">
-        <v>13.156</v>
+        <v>13.382</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.781</v>
+        <v>2.794</v>
       </c>
       <c r="AF47" t="n">
-        <v>9.061999999999999</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.307</v>
+        <v>0.314</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.062</v>
+        <v>2.059</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.781</v>
+        <v>5.912</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.357</v>
+        <v>0.348</v>
       </c>
       <c r="AK47" t="n">
-        <v>7</v>
+        <v>6.971</v>
       </c>
       <c r="AL47" t="n">
-        <v>21.219</v>
+        <v>21.294</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>84.465</v>
+        <v>84.554</v>
       </c>
       <c r="AP47" t="n">
         <v>0.522</v>
@@ -7646,22 +7646,22 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.963</v>
+        <v>0.961</v>
       </c>
       <c r="AS47" t="n">
         <v>0.145</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.255</v>
+        <v>0.252</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.253</v>
+        <v>1.225</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="AX47" t="n">
         <v>0.138</v>
@@ -7677,153 +7677,153 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
-        <v>85.625</v>
+        <v>86.235</v>
       </c>
       <c r="D48" t="n">
-        <v>20.219</v>
+        <v>20.588</v>
       </c>
       <c r="E48" t="n">
-        <v>36.406</v>
+        <v>36.706</v>
       </c>
       <c r="F48" t="n">
-        <v>9.218999999999999</v>
+        <v>9.147</v>
       </c>
       <c r="G48" t="n">
-        <v>25.062</v>
+        <v>25.147</v>
       </c>
       <c r="H48" t="n">
-        <v>17.531</v>
+        <v>17.618</v>
       </c>
       <c r="I48" t="n">
-        <v>23.094</v>
+        <v>23.235</v>
       </c>
       <c r="J48" t="n">
-        <v>16.344</v>
+        <v>16.265</v>
       </c>
       <c r="K48" t="n">
-        <v>25.5</v>
+        <v>25.765</v>
       </c>
       <c r="L48" t="n">
-        <v>10.438</v>
+        <v>10.324</v>
       </c>
       <c r="M48" t="n">
-        <v>7.344</v>
+        <v>7.382</v>
       </c>
       <c r="N48" t="n">
-        <v>5.312</v>
+        <v>5.176</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>13.125</v>
+        <v>12.882</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.094</v>
+        <v>11.912</v>
       </c>
       <c r="R48" t="n">
-        <v>22.344</v>
+        <v>22.206</v>
       </c>
       <c r="S48" t="n">
-        <v>21.75</v>
+        <v>21.735</v>
       </c>
       <c r="T48" t="n">
-        <v>3176</v>
+        <v>3402</v>
       </c>
       <c r="U48" t="n">
-        <v>10.75</v>
+        <v>10.824</v>
       </c>
       <c r="V48" t="n">
-        <v>9.593999999999999</v>
+        <v>9.676</v>
       </c>
       <c r="W48" t="n">
-        <v>4.469</v>
+        <v>4.853</v>
       </c>
       <c r="X48" t="n">
-        <v>3.031</v>
+        <v>3.176</v>
       </c>
       <c r="Y48" t="n">
-        <v>28.594</v>
+        <v>29.118</v>
       </c>
       <c r="Z48" t="n">
-        <v>37.969</v>
+        <v>38.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.75</v>
+        <v>5.676</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.625</v>
+        <v>12.647</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.455</v>
+        <v>0.449</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.406</v>
+        <v>3.412</v>
       </c>
       <c r="AF48" t="n">
-        <v>8.906000000000001</v>
+        <v>8.794</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.188</v>
+        <v>2.176</v>
       </c>
       <c r="AI48" t="n">
-        <v>5.719</v>
+        <v>5.735</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.383</v>
+        <v>0.379</v>
       </c>
       <c r="AK48" t="n">
-        <v>7.031</v>
+        <v>6.971</v>
       </c>
       <c r="AL48" t="n">
-        <v>19.344</v>
+        <v>19.412</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>84.755</v>
+        <v>84.959</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.554</v>
+        <v>0.555</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.598</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>1.015</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AT48" t="n">
         <v>0.285</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.245</v>
+        <v>1.263</v>
       </c>
       <c r="AV48" t="n">
         <v>0.201</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
